--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-09T07:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="425">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T07:17:44+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -271,6 +271,9 @@
     <t>ControlAct[moodCode=INT]</t>
   </si>
   <si>
+    <t>workflow.order</t>
+  </si>
+  <si>
     <t>Task.id</t>
   </si>
   <si>
@@ -354,7 +357,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -412,6 +415,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -452,7 +459,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -591,7 +598,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/task-status|4.3.0</t>
   </si>
   <si>
     <t>Request.status, Event.status</t>
@@ -662,7 +669,7 @@
     <t>Distinguishes whether the task is a proposal, plan or full order.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/task-intent|4.3.0</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -689,10 +696,10 @@
     <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
-    <t>The task's priority.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+    <t>The priority of a task (may affect service level applied to the task).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
   </si>
   <si>
     <t>Request.priority</t>
@@ -1118,6 +1125,10 @@
   </si>
   <si>
     <t>Sometimes when fulfillment is sought, you don't want full fulfillment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>Instead of pointing to request, would point to component of request, having these characteristics</t>
@@ -1914,7 +1925,7 @@
         <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>76</v>
@@ -1922,10 +1933,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1936,7 +1947,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>76</v>
@@ -1945,19 +1956,19 @@
         <v>76</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2007,13 +2018,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -2036,10 +2047,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2050,7 +2061,7 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>76</v>
@@ -2059,16 +2070,16 @@
         <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2119,19 +2130,19 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -2148,10 +2159,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2162,28 +2173,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2233,19 +2244,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2262,10 +2273,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2276,7 +2287,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -2288,16 +2299,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2323,13 +2334,13 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -2347,19 +2358,19 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2376,21 +2387,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -2402,16 +2413,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2461,25 +2472,25 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>76</v>
@@ -2490,14 +2501,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2516,16 +2527,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2575,7 +2586,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2587,13 +2598,13 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>76</v>
@@ -2604,14 +2615,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2630,16 +2641,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2689,7 +2700,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2701,13 +2712,13 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>76</v>
@@ -2718,14 +2729,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2738,25 +2749,25 @@
         <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2805,7 +2816,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2817,13 +2828,13 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>76</v>
@@ -2834,10 +2845,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2860,13 +2871,13 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2917,7 +2928,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2929,16 +2940,16 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>76</v>
@@ -2946,10 +2957,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2960,7 +2971,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
@@ -2969,20 +2980,20 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -3031,25 +3042,25 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>76</v>
@@ -3060,10 +3071,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3074,7 +3085,7 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -3083,20 +3094,20 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -3145,25 +3156,25 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>76</v>
@@ -3174,10 +3185,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3197,16 +3208,16 @@
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3257,7 +3268,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3269,13 +3280,13 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>76</v>
@@ -3286,10 +3297,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3300,7 +3311,7 @@
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>76</v>
@@ -3309,20 +3320,20 @@
         <v>76</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3371,25 +3382,25 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -3400,10 +3411,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3423,22 +3434,22 @@
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3487,7 +3498,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3499,13 +3510,13 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>76</v>
@@ -3516,10 +3527,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3527,32 +3538,32 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3577,52 +3588,52 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>76</v>
@@ -3630,10 +3641,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3644,7 +3655,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -3653,19 +3664,19 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3691,10 +3702,10 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>76</v>
@@ -3715,25 +3726,25 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>76</v>
@@ -3744,10 +3755,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3758,7 +3769,7 @@
         <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>76</v>
@@ -3767,20 +3778,20 @@
         <v>76</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3805,10 +3816,10 @@
         <v>76</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>76</v>
@@ -3829,25 +3840,25 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>76</v>
@@ -3858,10 +3869,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3869,10 +3880,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>76</v>
@@ -3881,19 +3892,19 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3919,13 +3930,13 @@
         <v>76</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>76</v>
@@ -3943,28 +3954,28 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>76</v>
@@ -3972,10 +3983,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3986,7 +3997,7 @@
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -3998,23 +4009,23 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="R21" t="s" s="2">
         <v>76</v>
@@ -4035,13 +4046,13 @@
         <v>76</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>76</v>
@@ -4059,28 +4070,28 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
@@ -4088,10 +4099,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4102,7 +4113,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>76</v>
@@ -4111,19 +4122,19 @@
         <v>76</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4149,13 +4160,13 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>76</v>
@@ -4173,28 +4184,28 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>76</v>
@@ -4202,10 +4213,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4216,7 +4227,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -4225,16 +4236,16 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4285,25 +4296,25 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4314,10 +4325,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4328,7 +4339,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>76</v>
@@ -4337,22 +4348,22 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4401,28 +4412,28 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
@@ -4430,21 +4441,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4453,20 +4464,20 @@
         <v>76</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4515,28 +4526,28 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>76</v>
@@ -4544,10 +4555,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4558,7 +4569,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4567,20 +4578,20 @@
         <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4629,28 +4640,28 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>76</v>
@@ -4658,10 +4669,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4669,10 +4680,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -4681,16 +4692,16 @@
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4741,28 +4752,28 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
@@ -4770,21 +4781,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4796,17 +4807,17 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4855,28 +4866,28 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>76</v>
@@ -4884,21 +4895,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4907,20 +4918,20 @@
         <v>76</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -4969,25 +4980,25 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>76</v>
@@ -4998,10 +5009,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5012,7 +5023,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -5021,20 +5032,20 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -5083,28 +5094,28 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>76</v>
@@ -5112,10 +5123,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5138,17 +5149,17 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5173,13 +5184,13 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -5197,7 +5208,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5209,16 +5220,16 @@
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>76</v>
@@ -5226,21 +5237,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -5249,22 +5260,22 @@
         <v>76</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5313,28 +5324,28 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>76</v>
@@ -5342,10 +5353,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5356,7 +5367,7 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>76</v>
@@ -5365,20 +5376,20 @@
         <v>76</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -5427,28 +5438,28 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>76</v>
@@ -5456,10 +5467,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5470,7 +5481,7 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>76</v>
@@ -5482,16 +5493,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5517,10 +5528,10 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>76</v>
@@ -5541,39 +5552,39 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5584,7 +5595,7 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
@@ -5596,16 +5607,16 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5655,28 +5666,28 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>76</v>
@@ -5684,10 +5695,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5710,13 +5721,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5767,7 +5778,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5779,27 +5790,27 @@
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5813,7 +5824,7 @@
         <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>76</v>
@@ -5822,13 +5833,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5879,7 +5890,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5891,13 +5902,13 @@
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>76</v>
@@ -5908,14 +5919,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5934,16 +5945,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5993,7 +6004,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6005,13 +6016,13 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>76</v>
@@ -6022,10 +6033,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6036,7 +6047,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -6048,17 +6059,17 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -6107,25 +6118,25 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>357</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -6136,10 +6147,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6150,7 +6161,7 @@
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -6162,13 +6173,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6219,13 +6230,13 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>76</v>
@@ -6237,7 +6248,7 @@
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6248,14 +6259,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6274,16 +6285,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6333,7 +6344,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6345,13 +6356,13 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6362,14 +6373,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6382,25 +6393,25 @@
         <v>76</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6449,7 +6460,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6461,13 +6472,13 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6478,10 +6489,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6492,7 +6503,7 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>76</v>
@@ -6504,17 +6515,17 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6563,25 +6574,25 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>76</v>
@@ -6592,10 +6603,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6606,7 +6617,7 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6618,19 +6629,19 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6679,25 +6690,25 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>76</v>
@@ -6708,10 +6719,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6734,13 +6745,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6791,7 +6802,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6803,13 +6814,13 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6820,14 +6831,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6846,17 +6857,17 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6905,7 +6916,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6917,13 +6928,13 @@
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>357</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>76</v>
@@ -6934,10 +6945,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6948,7 +6959,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -6960,13 +6971,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7017,13 +7028,13 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
@@ -7035,7 +7046,7 @@
         <v>76</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>76</v>
@@ -7046,14 +7057,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7072,16 +7083,16 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7131,7 +7142,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7143,13 +7154,13 @@
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>76</v>
@@ -7160,14 +7171,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7180,25 +7191,25 @@
         <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -7247,7 +7258,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7259,13 +7270,13 @@
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>76</v>
@@ -7276,21 +7287,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>76</v>
@@ -7302,19 +7313,19 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -7339,10 +7350,10 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>76</v>
@@ -7363,25 +7374,25 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>76</v>
@@ -7392,10 +7403,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7403,10 +7414,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>76</v>
@@ -7418,13 +7429,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7475,25 +7486,25 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>76</v>
@@ -7504,10 +7515,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7530,17 +7541,17 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7589,7 +7600,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7601,13 +7612,13 @@
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>357</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>76</v>
@@ -7618,10 +7629,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7632,7 +7643,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>76</v>
@@ -7644,13 +7655,13 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7701,13 +7712,13 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>76</v>
@@ -7719,7 +7730,7 @@
         <v>76</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>76</v>
@@ -7730,14 +7741,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7756,16 +7767,16 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7815,7 +7826,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7827,13 +7838,13 @@
         <v>76</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>76</v>
@@ -7844,14 +7855,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7864,25 +7875,25 @@
         <v>76</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7931,7 +7942,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7943,13 +7954,13 @@
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>76</v>
@@ -7960,21 +7971,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>76</v>
@@ -7986,17 +7997,17 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -8021,10 +8032,10 @@
         <v>76</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>76</v>
@@ -8045,25 +8056,25 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>76</v>
@@ -8074,10 +8085,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8085,10 +8096,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>
@@ -8100,17 +8111,17 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8159,25 +8170,25 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -271,9 +271,6 @@
     <t>ControlAct[moodCode=INT]</t>
   </si>
   <si>
-    <t>workflow.order</t>
-  </si>
-  <si>
     <t>Task.id</t>
   </si>
   <si>
@@ -357,7 +354,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -415,10 +412,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -459,7 +452,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -598,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/task-status|4.0.1</t>
   </si>
   <si>
     <t>Request.status, Event.status</t>
@@ -669,7 +662,7 @@
     <t>Distinguishes whether the task is a proposal, plan or full order.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-intent|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/task-intent|4.0.1</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -696,10 +689,10 @@
     <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
-    <t>The priority of a task (may affect service level applied to the task).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
+    <t>The task's priority.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
   </si>
   <si>
     <t>Request.priority</t>
@@ -1125,10 +1118,6 @@
   </si>
   <si>
     <t>Sometimes when fulfillment is sought, you don't want full fulfillment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>Instead of pointing to request, would point to component of request, having these characteristics</t>
@@ -1925,7 +1914,7 @@
         <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>76</v>
@@ -1933,10 +1922,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1947,28 +1936,28 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2018,13 +2007,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -2047,10 +2036,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2061,25 +2050,25 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2130,19 +2119,19 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -2159,10 +2148,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2173,28 +2162,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2244,19 +2233,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2273,10 +2262,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2287,7 +2276,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -2299,16 +2288,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2334,43 +2323,43 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2387,21 +2376,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -2413,16 +2402,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2472,25 +2461,25 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>76</v>
@@ -2501,14 +2490,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2527,16 +2516,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2586,7 +2575,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2598,13 +2587,13 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>76</v>
@@ -2615,14 +2604,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2641,16 +2630,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2700,7 +2689,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2712,13 +2701,13 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>76</v>
@@ -2729,14 +2718,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2749,25 +2738,25 @@
         <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2816,7 +2805,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2828,13 +2817,13 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>76</v>
@@ -2845,10 +2834,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2871,13 +2860,13 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2928,7 +2917,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2940,16 +2929,16 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>76</v>
@@ -2957,10 +2946,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2971,29 +2960,29 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -3042,25 +3031,25 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>76</v>
@@ -3071,10 +3060,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3085,29 +3074,29 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K13" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -3156,25 +3145,25 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>76</v>
@@ -3185,10 +3174,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3208,16 +3197,16 @@
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3268,7 +3257,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3280,13 +3269,13 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>76</v>
@@ -3297,10 +3286,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3311,29 +3300,29 @@
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J15" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3382,25 +3371,25 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -3411,10 +3400,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3434,22 +3423,22 @@
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3498,7 +3487,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3510,13 +3499,13 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>76</v>
@@ -3527,10 +3516,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3538,32 +3527,32 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G17" t="s" s="2">
+      <c r="J17" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3588,52 +3577,52 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>76</v>
@@ -3641,10 +3630,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3655,28 +3644,28 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3702,49 +3691,49 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>76</v>
@@ -3755,10 +3744,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3769,29 +3758,29 @@
         <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K19" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3816,10 +3805,10 @@
         <v>76</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>76</v>
@@ -3840,25 +3829,25 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>76</v>
@@ -3869,10 +3858,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3880,31 +3869,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3930,52 +3919,52 @@
         <v>76</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Z20" t="s" s="2">
+      <c r="AL20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AA20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>76</v>
@@ -3983,10 +3972,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3997,7 +3986,7 @@
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -4009,89 +3998,89 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y21" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="P21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q21" t="s" s="2">
+      <c r="Z21" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="R21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y21" t="s" s="2">
+      <c r="AA21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="Z21" t="s" s="2">
+      <c r="AL21" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AA21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
@@ -4099,10 +4088,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4113,28 +4102,28 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4160,52 +4149,52 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="Z22" t="s" s="2">
+      <c r="AL22" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AA22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>76</v>
@@ -4213,10 +4202,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4227,25 +4216,25 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4296,25 +4285,25 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4325,10 +4314,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4339,31 +4328,31 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4412,28 +4401,28 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
@@ -4441,43 +4430,43 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4526,28 +4515,28 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>76</v>
@@ -4555,10 +4544,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4569,29 +4558,29 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4640,28 +4629,28 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>76</v>
@@ -4669,10 +4658,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4680,28 +4669,28 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4752,28 +4741,28 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
@@ -4781,21 +4770,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4807,17 +4796,17 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4866,28 +4855,28 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>76</v>
@@ -4895,43 +4884,43 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -4980,25 +4969,25 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>76</v>
@@ -5009,10 +4998,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5023,29 +5012,29 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -5094,28 +5083,28 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>76</v>
@@ -5123,10 +5112,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5149,17 +5138,17 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5184,13 +5173,13 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -5208,7 +5197,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5220,16 +5209,16 @@
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>76</v>
@@ -5237,45 +5226,45 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K32" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5324,28 +5313,28 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>76</v>
@@ -5353,10 +5342,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5367,29 +5356,29 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K33" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -5438,28 +5427,28 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>76</v>
@@ -5467,10 +5456,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5481,7 +5470,7 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>76</v>
@@ -5493,16 +5482,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5528,63 +5517,63 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5595,7 +5584,7 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
@@ -5607,16 +5596,16 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5666,28 +5655,28 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>76</v>
@@ -5695,10 +5684,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5721,13 +5710,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5778,7 +5767,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5790,27 +5779,27 @@
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5824,7 +5813,7 @@
         <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>76</v>
@@ -5833,13 +5822,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5890,7 +5879,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5902,13 +5891,13 @@
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>76</v>
@@ -5919,14 +5908,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5945,16 +5934,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6004,7 +5993,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6016,13 +6005,13 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>76</v>
@@ -6033,10 +6022,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6047,7 +6036,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -6059,17 +6048,17 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -6118,25 +6107,25 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>357</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -6147,10 +6136,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6161,7 +6150,7 @@
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -6173,13 +6162,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6230,13 +6219,13 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>76</v>
@@ -6248,7 +6237,7 @@
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6259,14 +6248,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6285,16 +6274,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6344,7 +6333,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6356,13 +6345,13 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6373,14 +6362,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6393,25 +6382,25 @@
         <v>76</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6460,7 +6449,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6472,13 +6461,13 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6489,10 +6478,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6503,7 +6492,7 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>76</v>
@@ -6515,17 +6504,17 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6574,25 +6563,25 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>76</v>
@@ -6603,10 +6592,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6617,7 +6606,7 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6629,19 +6618,19 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6690,25 +6679,25 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>76</v>
@@ -6719,10 +6708,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6745,13 +6734,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6802,7 +6791,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6814,13 +6803,13 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6831,14 +6820,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6857,17 +6846,17 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6916,7 +6905,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6928,13 +6917,13 @@
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>357</v>
+        <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>76</v>
@@ -6945,10 +6934,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6959,7 +6948,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -6971,13 +6960,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7028,13 +7017,13 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
@@ -7046,7 +7035,7 @@
         <v>76</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>76</v>
@@ -7057,14 +7046,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7083,16 +7072,16 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7142,7 +7131,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7154,13 +7143,13 @@
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>76</v>
@@ -7171,14 +7160,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7191,25 +7180,25 @@
         <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -7258,7 +7247,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7270,13 +7259,13 @@
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>76</v>
@@ -7287,21 +7276,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>76</v>
@@ -7313,19 +7302,19 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -7350,10 +7339,10 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>76</v>
@@ -7374,25 +7363,25 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>76</v>
@@ -7403,10 +7392,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7414,10 +7403,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>76</v>
@@ -7429,13 +7418,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7486,25 +7475,25 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>76</v>
@@ -7515,10 +7504,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7541,17 +7530,17 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7600,7 +7589,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7612,13 +7601,13 @@
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>357</v>
+        <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>76</v>
@@ -7629,10 +7618,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7643,7 +7632,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>76</v>
@@ -7655,13 +7644,13 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7712,13 +7701,13 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>76</v>
@@ -7730,7 +7719,7 @@
         <v>76</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>76</v>
@@ -7741,14 +7730,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7767,16 +7756,16 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7826,7 +7815,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7838,13 +7827,13 @@
         <v>76</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>76</v>
@@ -7855,14 +7844,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7875,25 +7864,25 @@
         <v>76</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7942,7 +7931,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7954,13 +7943,13 @@
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>76</v>
@@ -7971,21 +7960,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>76</v>
@@ -7997,17 +7986,17 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -8032,10 +8021,10 @@
         <v>76</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>76</v>
@@ -8056,25 +8045,25 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>76</v>
@@ -8085,10 +8074,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8096,10 +8085,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>
@@ -8111,17 +8100,17 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8170,25 +8159,25 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$64</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2344" uniqueCount="450">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:35:55+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -237,13 +237,13 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: HL7 v2 Mapping</t>
+    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t/>
@@ -268,7 +268,10 @@
     <t>Request, Event</t>
   </si>
   <si>
-    <t>ControlAct[moodCode=INT]</t>
+    <t>workflow.order</t>
+  </si>
+  <si>
+    <t>Entity, Role, or Act,ControlAct[moodCode=INT]</t>
   </si>
   <si>
     <t>Task.id</t>
@@ -290,7 +293,7 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -329,7 +332,7 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -351,13 +354,13 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -380,10 +383,14 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-6
+</t>
   </si>
   <si>
     <t>Act.text?</t>
@@ -403,13 +410,17 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>N/A</t>
@@ -429,7 +440,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -448,11 +459,11 @@
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -474,10 +485,10 @@
     <t>Request.identifier, Event.identifier</t>
   </si>
   <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
     <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
   </si>
   <si>
     <t>Task.instantiatesCanonical</t>
@@ -493,7 +504,7 @@
     <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
   </si>
   <si>
-    <t>Enables a formal definition of how he task is to be performed, enabling automation.</t>
+    <t>Enables a formal definition of how the task is to be performed, enabling automation.</t>
   </si>
   <si>
     <t>Request.instantiatesCanonical, Event.instantiatesCanonical</t>
@@ -508,10 +519,10 @@
     <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
   </si>
   <si>
-    <t>Enables a formal definition of how he task is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a task), enabling automation.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesUrl</t>
+    <t>Enables a formal definition of how the task is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a task), enabling automation.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesUri</t>
   </si>
   <si>
     <t>Task.basedOn</t>
@@ -524,7 +535,10 @@
     <t>Request fulfilled by this task</t>
   </si>
   <si>
-    <t>BasedOn refers to a higher-level authorization that triggered the creation of the task.  It references a "request" resource such as a ServiceRequest, MedicationRequest, ServiceRequest, CarePlan, etc. which is distinct from the "request" resource the task is seeking to fulfill.  This latter resource is referenced by FocusOn.  For example, based on a ServiceRequest (= BasedOn), a task is created to fulfill a procedureRequest ( = FocusOn ) to collect a specimen from a patient.</t>
+    <t>BasedOn refers to a higher-level authorization that triggered the creation of the task.  It references a "request" resource such as a ServiceRequest, MedicationRequest, CarePlan, etc. which is distinct from the "request" resource the task is seeking to fulfill.  This latter resource is referenced by focus.  For example, based on a CarePlan (= basedOn), a task is created to fulfill a ServiceRequest ( = focus ) to collect a specimen from a patient.</t>
+  </si>
+  <si>
+    <t>Task.basedOn is never the same as Task.focus.  Task.basedOn will typically not be present for 'please fulfill' Tasks as a distinct authorization is rarely needed to request fulfillment.  If the Task is seeking fulfillment of an order, the order to be fulfilled is always communicated using `focus`, never basedOn.  However, authorization may be needed to perform other types of Task actions.  As an example of when both would be present, a Task seeking suspension of a prescription might have a Task.basedOn pointing to the ServiceRequest ordering surgery (which is the driver for suspending the MedicationRequest - which would be the Task.focus).</t>
   </si>
   <si>
     <t>Request.basedOn, Event.basedOn</t>
@@ -539,7 +553,7 @@
     <t>Requisition or grouper id</t>
   </si>
   <si>
-    <t>An identifier that links together multiple tasks and other requests that were created in the same context.</t>
+    <t>A shared identifier common to multiple independent Task and Request instances that were activated/authorized more or less simultaneously by a single author.  The presence of the same identifier on each request ties those requests together and may have business ramifications in terms of reporting of results, billing, etc.  E.g. a requisition number shared by a set of lab tests ordered together, or a prescription number shared by all meds ordered at one time.</t>
   </si>
   <si>
     <t>Billing and/or reporting can be linked to whether multiple requests were created as a single unit.</t>
@@ -588,49 +602,53 @@
     <t>These states enable coordination of task status with off-the-shelf workflow solutions that support automation of tasks.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/task-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/task-status|5.0.0</t>
   </si>
   <si>
     <t>Request.status, Event.status</t>
   </si>
   <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
     <t>.statusCode</t>
   </si>
   <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
     <t>Task.statusReason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference
+</t>
+  </si>
+  <si>
+    <t>Reason for current status</t>
+  </si>
+  <si>
+    <t>An explanation as to why this task is held, failed, was refused, etc.</t>
+  </si>
+  <si>
+    <t>This applies to the current status.  Look at the history of the task to see reasons for past statuses.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes to identify the reason for current status.  These will typically be specific to a particular workflow.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/task-status-reason</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
+  </si>
+  <si>
+    <t>Task.businessStatus</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Reason for current status</t>
-  </si>
-  <si>
-    <t>An explanation as to why this task is held, failed, was refused, etc.</t>
-  </si>
-  <si>
-    <t>This applies to the current status.  Look at the history of the task to see reasons for past statuses.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes to identify the reason for current status.  These will typically be specific to a particular workflow.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
-  </si>
-  <si>
-    <t>Task.businessStatus</t>
-  </si>
-  <si>
     <t>E.g. "Specimen collected", "IV prepped"</t>
   </si>
   <si>
@@ -662,18 +680,18 @@
     <t>Distinguishes whether the task is a proposal, plan or full order.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/task-intent|5.0.0</t>
   </si>
   <si>
     <t>Request.intent</t>
   </si>
   <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
     <t>.moodCode</t>
   </si>
   <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Task.priority</t>
   </si>
   <si>
@@ -689,19 +707,46 @@
     <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
-    <t>The task's priority.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+    <t>The priority of a task (may affect service level applied to the task).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|5.0.0</t>
   </si>
   <si>
     <t>Request.priority</t>
   </si>
   <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
     <t>.priorityCode</t>
   </si>
   <si>
-    <t>FiveWs.grade</t>
+    <t>Task.doNotPerform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>True if Task is prohibiting action</t>
+  </si>
+  <si>
+    <t>If true indicates that the Task is asking for the specified action to *not* occur.</t>
+  </si>
+  <si>
+    <t>The attributes provided with the Task qualify what is not to be done. For example, if a requestedPeriod is provided, the 'do not' request only applies within the specified time. If a requestedPerformer is specified then the 'do not' request only applies to performers of that type. Qualifiers include: code, subject, occurrence, requestedPerformer and performer.
+In some cases, the Request.code may pre-coordinate prohibition into the requested action. E.g. 'NPO' (nothing by mouth), 'DNR' (do not recussitate). If this happens, doNotPerform SHALL NOT be set to true. I.e. The resource shall not have double negation. (E.g. 'Do not DNR').
+doNotPerform should ONLY be used with Tasks that are tightly bounded in time or process phase.  E.g. 'Do not fulfill the midnight dose of medication X tonight due to the early morning scheduled procedure, where the nurse could reasonably check off 'Med X not given at midnight as instructed'.  Similarly, a decision support proposal that a patient should not be given a standard intake questionnaire (because the patient is cognitively impaired) would be marked as 'complete' or 'rejected' when the clinician preps the CarePlan or order set after reviewing the decision support results.  If there is a need to create a standing order to not do something that can't be satisfied by a single 'non-action', but rather an ongoing refusal to perform the function, MedicationRequest, ServiceRequest or some other form of authorization should be used.</t>
+  </si>
+  <si>
+    <t>Request.code, Event.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>.code</t>
   </si>
   <si>
     <t>Task.code</t>
@@ -722,13 +767,8 @@
     <t>http://hl7.org/fhir/ValueSet/task-code</t>
   </si>
   <si>
-    <t>Request.code, Event.code</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
+    <t xml:space="preserve">tsk-1
+</t>
   </si>
   <si>
     <t>Task.description</t>
@@ -753,7 +793,7 @@
     <t>What task is acting on</t>
   </si>
   <si>
-    <t>The request being actioned or the resource being manipulated by this task.</t>
+    <t>The request being fulfilled or the resource being manipulated (changed, suspended, etc.) by this task.</t>
   </si>
   <si>
     <t>If multiple resources need to be manipulated, use sub-tasks.  (This ensures that status can be tracked independently for each referenced resource.).</t>
@@ -784,10 +824,10 @@
     <t>Request.subject, Event.subject</t>
   </si>
   <si>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
     <t>.participation[typeCode=RCT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
   </si>
   <si>
     <t>Task.encounter</t>
@@ -806,22 +846,40 @@
     <t>For some tasks it may be important to know the link between the encounter the task originated within.</t>
   </si>
   <si>
-    <t>Request.context, Event.context</t>
+    <t>Request.encounter, Event.encounter</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=PCPR, moodCode=EVN]</t>
   </si>
   <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Task.executionPeriod</t>
+    <t>Task.requestedPeriod</t>
   </si>
   <si>
     <t xml:space="preserve">Period
 </t>
   </si>
   <si>
+    <t>When the task should be performed</t>
+  </si>
+  <si>
+    <t>Indicates the start and/or end of the period of time when completion of the task is desired to take place.</t>
+  </si>
+  <si>
+    <t>This is typically used when the Task is *not* seeking fulfillment of a focus Request, as in that case the period would be specified on the Request and/or in the Task.restriction.period.  Instead, it is used for stand-alone tasks.</t>
+  </si>
+  <si>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>Task.executionPeriod</t>
+  </si>
+  <si>
     <t>Start and end time of execution</t>
   </si>
   <si>
@@ -829,9 +887,6 @@
   </si>
   <si>
     <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
   </si>
   <si>
     <t>FiveWs.done[x]</t>
@@ -864,10 +919,10 @@
     <t>Request.authoredOn</t>
   </si>
   <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
     <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
   </si>
   <si>
     <t>Task.lastModified</t>
@@ -908,37 +963,44 @@
     <t>Request.requester</t>
   </si>
   <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
     <t>.participation[typeCode=AUT].role</t>
   </si>
   <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>Task.performerType</t>
-  </si>
-  <si>
-    <t>Requested performer</t>
-  </si>
-  <si>
-    <t>The kind of participant that should perform the task.</t>
+    <t>Task.requestedPerformer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Who should perform Task</t>
+  </si>
+  <si>
+    <t>The kind of participant or specific participant that should perform the task.</t>
   </si>
   <si>
     <t>Use to distinguish tasks on different activity queues.</t>
   </si>
   <si>
+    <t>preferred</t>
+  </si>
+  <si>
     <t>The type(s) of task performers allowed.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/performer-role</t>
   </si>
   <si>
-    <t>Event.performer.role, Request.performerType</t>
+    <t>Event.performer.function, Request.performerType</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>.participation[typeCode=PRF].role.code</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>Task.owner</t>
@@ -948,14 +1010,14 @@
 Executer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
     <t>Responsible individual</t>
   </si>
   <si>
-    <t>Individual organization or Device currently responsible for task execution.</t>
+    <t>Party responsible for managing task execution.</t>
   </si>
   <si>
     <t>Tasks may be created with an owner not yet identified.</t>
@@ -968,6 +1030,85 @@
   </si>
   <si>
     <t>.participation[typeCode=PRF].role</t>
+  </si>
+  <si>
+    <t>Task.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Who or what performed the task</t>
+  </si>
+  <si>
+    <t>The entity who performed the requested task.</t>
+  </si>
+  <si>
+    <t>Task.performer.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Task.performer.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Task.performer.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Task.performer.function</t>
+  </si>
+  <si>
+    <t>Type of performance</t>
+  </si>
+  <si>
+    <t>A code or description of the performer of the task.</t>
+  </si>
+  <si>
+    <t>Codes to identify types of task performers.</t>
+  </si>
+  <si>
+    <t>Task.performer.actor</t>
+  </si>
+  <si>
+    <t>Who performed the task</t>
+  </si>
+  <si>
+    <t>The actor or entity who performed the task.</t>
   </si>
   <si>
     <t>Task.location</t>
@@ -980,61 +1121,46 @@
     <t>Where task occurs</t>
   </si>
   <si>
-    <t>Principal physical location where the this task is performed.</t>
+    <t>Principal physical location where this task is performed.</t>
+  </si>
+  <si>
+    <t>This should only be specified when the Task to be/being performed happens or is expected to happen primarily within the bounds of a single Location.  Other locations (e.g. source, destination, etc.) would either be reflected on the 'basedOn' Request or be conveyed as distinct Task.input values.</t>
   </si>
   <si>
     <t>Ties the event to where the records are likely kept and provides context around the event occurrence (e.g. if it occurred inside or outside a dedicated healthcare setting).</t>
   </si>
   <si>
-    <t>Request.reasonCode, Event.reasonCode</t>
+    <t>FiveWs.where[x]</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role</t>
   </si>
   <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>Task.reasonCode</t>
+    <t>Task.reason</t>
   </si>
   <si>
     <t>Why task is needed</t>
   </si>
   <si>
-    <t>A description or code indicating why this task needs to be performed.</t>
-  </si>
-  <si>
-    <t>This should only be included if there is no focus or if it differs from the reason indicated on the focus.</t>
+    <t>A description, code, or reference indicating why this task needs to be performed.</t>
+  </si>
+  <si>
+    <t>This will typically not be present for Tasks with a code of 'please fulfill' as, for those, the reason for action is conveyed on the Request pointed to by Task.focus.  Some types of tasks will not need a 'reason'.  E.g. a request to discharge a patient can be inferred to be 'because the patient is ready' and this would not need a reason to be stated on the Task.</t>
   </si>
   <si>
     <t>Indicates why the task is needed.  E.g. Suspended because patient admitted to hospital.</t>
   </si>
   <si>
-    <t>Event.location</t>
+    <t>Event.reason, Request.reason</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
   </si>
   <si>
     <t>.reasonCode</t>
   </si>
   <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
     <t>EVN.7</t>
-  </si>
-  <si>
-    <t>Task.reasonReference</t>
-  </si>
-  <si>
-    <t>A resource reference indicating why this task needs to be performed.</t>
-  </si>
-  <si>
-    <t>Tasks might be justified based on an Observation, a Condition, a past or planned procedure, etc.   This should only be included if there is no focus or if it differs from the reason indicated on the focus.    Use the CodeableConcept text element in `Task.reasonCode` if the data is free (uncoded) text.</t>
-  </si>
-  <si>
-    <t>Request.reasonReference, Event.reasonReference</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON].target</t>
   </si>
   <si>
     <t>Task.insurance</t>
@@ -1107,16 +1233,15 @@
     <t>Task.restriction</t>
   </si>
   <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
     <t>Constraints on fulfillment tasks</t>
   </si>
   <si>
     <t>If the Task.focus is a request resource and the task is seeking fulfillment (i.e. is asking for the request to be actioned), this element identifies any limitations on what parts of the referenced request should be actioned.</t>
   </si>
   <si>
+    <t>Task.restriction can only be present if the Task is seeking fulfillment of another Request resource, and the restriction identifies what subset of the authorization conveyed by the request is supposed to be fulfilled by this Task. A possible example could be a standing order (the request) covering a significant time period and/or individuals, while the Task seeks fulfillment for only a subset of that time-period and a single individual.</t>
+  </si>
+  <si>
     <t>Sometimes when fulfillment is sought, you don't want full fulfillment.</t>
   </si>
   <si>
@@ -1126,42 +1251,10 @@
     <t>Task.restriction.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Task.restriction.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Task.restriction.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
     <t>Task.restriction.repetitions</t>
@@ -1186,13 +1279,14 @@
     <t>Task.restriction.period</t>
   </si>
   <si>
-    <t>When fulfillment sought</t>
-  </si>
-  <si>
-    <t>Over what time-period is fulfillment sought.</t>
-  </si>
-  <si>
-    <t>Note that period.high is the due date representing the time by which the task should be completed.</t>
+    <t>When fulfillment is sought</t>
+  </si>
+  <si>
+    <t>The time-period for which fulfillment is sought. This must fall within the overall time period authorized in the referenced request.  E.g. ServiceRequest.occurance[x].</t>
+  </si>
+  <si>
+    <t>This is distinct from Task.executionPeriod. ExecutionPeriod indicates when the task needs to be initiated, while Task.restriction.period specifies the subset of the overall authorization that this period covers. For example, a MedicationRequest with an overall effective period of 1 year might have a Task whose restriction.period is 2 months (i.e. satisfy 2 months of medication therapy), while the execution period might be 'between now and 5 days from now' - i.e. If you say yes to this, then you're agreeing to supply medication for that 2 month period within the next 5 days.
+Note that period.high is the due date representing the time by which the task should be completed.</t>
   </si>
   <si>
     <t>E.g. order that authorizes 1 year's services.  Fulfillment is sought for next 3 months.</t>
@@ -1211,7 +1305,7 @@
     <t>For whom is fulfillment sought?</t>
   </si>
   <si>
-    <t>For requests that are targeted to more than on potential recipient/target, for whom is fulfillment sought?</t>
+    <t>For requests that are targeted to more than one potential recipient/target, to identify who is fulfillment is sought for.</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role</t>
@@ -1271,7 +1365,7 @@
   </si>
   <si>
     <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+booleancanonicalcodedatedateTimedecimalidinstantintegerinteger64markdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodeableReferenceCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioRatioRangeReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextAvailabilityExtendedContactDetailDosageMeta</t>
   </si>
   <si>
     <t>Content to use in performing the task</t>
@@ -1474,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1561,77 +1655,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>25</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>35</v>
       </c>
     </row>
@@ -1642,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN57"/>
+  <dimension ref="A1:AN64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.42578125" customWidth="true" bestFit="true"/>
@@ -1681,9 +1783,9 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="55.72265625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="109.98828125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="109.98828125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.37109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1914,7 +2016,7 @@
         <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>76</v>
@@ -1922,10 +2024,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1936,7 +2038,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>76</v>
@@ -1945,19 +2047,19 @@
         <v>76</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2007,13 +2109,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -2036,10 +2138,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2050,7 +2152,7 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>76</v>
@@ -2059,16 +2161,16 @@
         <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2119,19 +2221,19 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -2148,10 +2250,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2162,28 +2264,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2233,19 +2335,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2262,10 +2364,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2276,7 +2378,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -2288,16 +2390,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2323,13 +2425,13 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -2347,19 +2449,19 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2376,21 +2478,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -2402,16 +2504,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2461,28 +2563,28 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>76</v>
@@ -2490,14 +2592,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2516,16 +2618,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2575,7 +2677,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2584,7 +2686,7 @@
         <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>76</v>
@@ -2593,10 +2695,10 @@
         <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>76</v>
@@ -2604,14 +2706,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2630,16 +2732,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2689,7 +2791,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2701,16 +2803,16 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>76</v>
@@ -2718,14 +2820,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2738,25 +2840,25 @@
         <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2805,7 +2907,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2817,16 +2919,16 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>76</v>
@@ -2834,10 +2936,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2860,13 +2962,13 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2917,7 +3019,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2929,16 +3031,16 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>76</v>
@@ -2946,10 +3048,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2960,7 +3062,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
@@ -2969,20 +3071,20 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -3031,28 +3133,28 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>76</v>
@@ -3060,10 +3162,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3074,7 +3176,7 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -3083,20 +3185,20 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -3145,28 +3247,28 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>76</v>
@@ -3174,10 +3276,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3197,18 +3299,20 @@
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -3257,7 +3361,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3269,16 +3373,16 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>76</v>
@@ -3286,10 +3390,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3300,7 +3404,7 @@
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>76</v>
@@ -3309,20 +3413,20 @@
         <v>76</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3371,28 +3475,28 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>76</v>
@@ -3400,10 +3504,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3423,22 +3527,22 @@
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3487,7 +3591,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3499,16 +3603,16 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>76</v>
+        <v>183</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>76</v>
@@ -3516,10 +3620,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3527,32 +3631,32 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3577,52 +3681,52 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>76</v>
@@ -3630,10 +3734,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3644,7 +3748,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -3653,19 +3757,19 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3691,13 +3795,13 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3715,28 +3819,28 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>76</v>
@@ -3744,10 +3848,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3758,7 +3862,7 @@
         <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>76</v>
@@ -3767,20 +3871,20 @@
         <v>76</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3805,52 +3909,52 @@
         <v>76</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Z19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>197</v>
-      </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>76</v>
@@ -3858,10 +3962,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3869,10 +3973,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>76</v>
@@ -3881,19 +3985,19 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3919,52 +4023,52 @@
         <v>76</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Z20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AA20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>203</v>
-      </c>
       <c r="AG20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>76</v>
@@ -3972,10 +4076,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3986,7 +4090,7 @@
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -3998,23 +4102,23 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q21" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="R21" t="s" s="2">
         <v>76</v>
@@ -4035,52 +4139,52 @@
         <v>76</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
@@ -4088,10 +4192,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4102,28 +4206,28 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4149,52 +4253,52 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>226</v>
+        <v>76</v>
       </c>
       <c r="Z22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AA22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>76</v>
@@ -4202,10 +4306,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4216,7 +4320,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -4225,18 +4329,20 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4261,13 +4367,13 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>76</v>
+        <v>239</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>76</v>
@@ -4285,28 +4391,28 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>76</v>
+        <v>232</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>76</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>76</v>
@@ -4314,10 +4420,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4328,7 +4434,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>76</v>
@@ -4337,23 +4443,19 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>76</v>
       </c>
@@ -4401,28 +4503,28 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
@@ -4430,21 +4532,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4453,20 +4555,22 @@
         <v>76</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4515,28 +4619,28 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>76</v>
@@ -4544,21 +4648,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>76</v>
+        <v>254</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4567,20 +4671,20 @@
         <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>164</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4629,28 +4733,28 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>76</v>
@@ -4658,10 +4762,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4669,10 +4773,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -4681,19 +4785,21 @@
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
       </c>
@@ -4741,28 +4847,28 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
@@ -4770,21 +4876,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4793,21 +4899,21 @@
         <v>76</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
       </c>
@@ -4855,28 +4961,28 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>271</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>76</v>
@@ -4884,21 +4990,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>276</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4907,10 +5013,10 @@
         <v>76</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>277</v>
@@ -4919,9 +5025,7 @@
         <v>278</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>279</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
@@ -4969,28 +5073,28 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>271</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>76</v>
+        <v>279</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>280</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>76</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>76</v>
@@ -5005,14 +5109,14 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>76</v>
+        <v>282</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -5021,20 +5125,20 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -5089,22 +5193,22 @@
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>287</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>76</v>
@@ -5112,21 +5216,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>76</v>
+        <v>292</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>76</v>
@@ -5135,20 +5239,20 @@
         <v>76</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>190</v>
+        <v>283</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5173,13 +5277,13 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>293</v>
+        <v>76</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>294</v>
+        <v>76</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -5197,28 +5301,28 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>287</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>76</v>
@@ -5226,21 +5330,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>299</v>
+        <v>76</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -5249,22 +5353,20 @@
         <v>76</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5313,28 +5415,28 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>76</v>
@@ -5342,10 +5444,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5356,7 +5458,7 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>76</v>
@@ -5365,20 +5467,20 @@
         <v>76</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -5403,13 +5505,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>76</v>
+        <v>310</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>76</v>
+        <v>311</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>76</v>
+        <v>312</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5427,28 +5529,28 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>76</v>
@@ -5456,21 +5558,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>76</v>
+        <v>317</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>76</v>
@@ -5479,21 +5581,23 @@
         <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>190</v>
+        <v>318</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
@@ -5517,10 +5621,10 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>319</v>
+        <v>76</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>76</v>
@@ -5541,39 +5645,39 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>323</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5584,7 +5688,7 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
@@ -5593,20 +5697,18 @@
         <v>76</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>326</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5655,28 +5757,28 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>327</v>
+        <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>328</v>
+        <v>76</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>322</v>
+        <v>76</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>76</v>
@@ -5698,7 +5800,7 @@
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>76</v>
@@ -5710,13 +5812,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5767,43 +5869,43 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>333</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>333</v>
+        <v>76</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AM36" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AN36" t="s" s="2">
-        <v>335</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5813,7 +5915,7 @@
         <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>76</v>
@@ -5822,15 +5924,17 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>337</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5879,7 +5983,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5891,16 +5995,16 @@
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>340</v>
+        <v>76</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>341</v>
+        <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>76</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>76</v>
@@ -5908,14 +6012,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5928,24 +6032,26 @@
         <v>76</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>344</v>
+        <v>134</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>76</v>
       </c>
@@ -6005,16 +6111,16 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>348</v>
+        <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>349</v>
+        <v>76</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>76</v>
@@ -6022,10 +6128,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6036,7 +6142,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -6045,21 +6151,19 @@
         <v>76</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>351</v>
+        <v>202</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>354</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
       </c>
@@ -6083,10 +6187,10 @@
         <v>76</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>76</v>
+        <v>346</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>76</v>
@@ -6107,25 +6211,25 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>355</v>
+        <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -6136,10 +6240,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6147,10 +6251,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -6159,16 +6263,16 @@
         <v>76</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>232</v>
+        <v>318</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6219,25 +6323,25 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6248,21 +6352,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>76</v>
@@ -6271,21 +6375,23 @@
         <v>76</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>131</v>
+        <v>351</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>132</v>
+        <v>352</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
@@ -6333,28 +6439,28 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>76</v>
+        <v>357</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>76</v>
@@ -6362,14 +6468,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>365</v>
+        <v>76</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6382,26 +6488,24 @@
         <v>76</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
       </c>
@@ -6425,10 +6529,10 @@
         <v>76</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>76</v>
+        <v>362</v>
       </c>
       <c r="Z42" t="s" s="2">
         <v>76</v>
@@ -6449,7 +6553,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6461,27 +6565,27 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>76</v>
+        <v>363</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>128</v>
+        <v>364</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>76</v>
+        <v>365</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>76</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6492,7 +6596,7 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>76</v>
@@ -6504,18 +6608,16 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>373</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>76</v>
       </c>
@@ -6563,39 +6665,39 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>76</v>
+        <v>371</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>374</v>
+        <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>76</v>
+        <v>372</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>76</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6606,10 +6708,10 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>76</v>
@@ -6618,7 +6720,7 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>259</v>
+        <v>375</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>376</v>
@@ -6626,12 +6728,8 @@
       <c r="M44" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>379</v>
-      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>76</v>
       </c>
@@ -6679,28 +6777,28 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>76</v>
+        <v>378</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>380</v>
+        <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>76</v>
@@ -6708,14 +6806,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>76</v>
+        <v>381</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6742,7 +6840,9 @@
       <c r="M45" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N45" s="2"/>
+      <c r="N45" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6791,7 +6891,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6803,16 +6903,16 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>76</v>
+        <v>386</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>385</v>
+        <v>76</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>76</v>
+        <v>387</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>76</v>
@@ -6820,21 +6920,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>387</v>
+        <v>76</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>76</v>
@@ -6846,17 +6946,19 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6905,28 +7007,28 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>76</v>
@@ -6934,10 +7036,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6948,7 +7050,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -6960,13 +7062,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7017,16 +7119,16 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>76</v>
+        <v>333</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>76</v>
@@ -7035,10 +7137,10 @@
         <v>76</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>76</v>
+        <v>334</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>76</v>
@@ -7046,14 +7148,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7072,16 +7174,16 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7131,7 +7233,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7143,16 +7245,16 @@
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>76</v>
+        <v>334</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>76</v>
@@ -7160,14 +7262,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7180,25 +7282,25 @@
         <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -7247,7 +7349,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7259,16 +7361,16 @@
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>76</v>
@@ -7276,21 +7378,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>396</v>
+        <v>76</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>76</v>
@@ -7302,19 +7404,17 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>398</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -7339,10 +7439,10 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>401</v>
+        <v>76</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>76</v>
@@ -7363,28 +7463,28 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>76</v>
+        <v>402</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>76</v>
@@ -7392,10 +7492,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7403,10 +7503,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>76</v>
@@ -7418,7 +7518,7 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>403</v>
+        <v>270</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>404</v>
@@ -7426,8 +7526,12 @@
       <c r="M51" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="N51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>76</v>
       </c>
@@ -7475,28 +7579,28 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>76</v>
+        <v>408</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>76</v>
@@ -7504,10 +7608,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7530,18 +7634,16 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>409</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>76</v>
       </c>
@@ -7589,7 +7691,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7601,16 +7703,16 @@
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>76</v>
+        <v>413</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>76</v>
@@ -7618,21 +7720,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>76</v>
+        <v>415</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>76</v>
@@ -7644,16 +7746,18 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>232</v>
+        <v>326</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>358</v>
+        <v>417</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
       </c>
@@ -7701,28 +7805,28 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>359</v>
+        <v>414</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>76</v>
+        <v>419</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>76</v>
@@ -7730,21 +7834,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>76</v>
@@ -7756,17 +7860,15 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>132</v>
+        <v>330</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>76</v>
@@ -7815,28 +7917,28 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>333</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>76</v>
+        <v>334</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>76</v>
@@ -7844,14 +7946,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>365</v>
+        <v>133</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7864,26 +7966,24 @@
         <v>76</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>135</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
       </c>
@@ -7931,7 +8031,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7943,16 +8043,16 @@
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>76</v>
+        <v>334</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>76</v>
@@ -7960,43 +8060,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>396</v>
+        <v>339</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>414</v>
+        <v>340</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>416</v>
+        <v>143</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -8021,10 +8123,10 @@
         <v>76</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>417</v>
+        <v>76</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>76</v>
@@ -8045,28 +8147,28 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>413</v>
+        <v>342</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>76</v>
@@ -8074,21 +8176,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>76</v>
+        <v>424</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>
@@ -8100,17 +8202,19 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>403</v>
+        <v>202</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8135,10 +8239,10 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>76</v>
+        <v>429</v>
       </c>
       <c r="Z57" t="s" s="2">
         <v>76</v>
@@ -8159,35 +8263,831 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>76</v>
+        <v>419</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN57">
+  <autoFilter ref="A1:AN64">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8197,7 +9097,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI63">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/result-dispatched-to-facility</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/result-dispatched-to-facility</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/result-dispatched-to-facility</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/result-dispatched-to-facility</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2344" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="423">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,13 +105,13 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Task</t>
+    <t>Transport</t>
   </si>
   <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Task</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Transport</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -259,22 +259,22 @@
 </t>
   </si>
   <si>
-    <t>A task to be performed</t>
-  </si>
-  <si>
-    <t>A task to be performed.</t>
-  </si>
-  <si>
-    <t>Request, Event</t>
+    <t>Delivery of item</t>
+  </si>
+  <si>
+    <t>Record of transport of item.</t>
+  </si>
+  <si>
+    <t>Event,Request</t>
   </si>
   <si>
     <t>workflow.order</t>
   </si>
   <si>
-    <t>Entity, Role, or Act,ControlAct[moodCode=INT]</t>
-  </si>
-  <si>
-    <t>Task.id</t>
+    <t>Entity, Role, or Act,Supply[moodCode=RQO]</t>
+  </si>
+  <si>
+    <t>Transport.id</t>
   </si>
   <si>
     <t>1</t>
@@ -299,7 +299,7 @@
     <t>Resource.id</t>
   </si>
   <si>
-    <t>Task.meta</t>
+    <t>Transport.meta</t>
   </si>
   <si>
     <t xml:space="preserve">Meta
@@ -319,7 +319,7 @@
 </t>
   </si>
   <si>
-    <t>Task.implicitRules</t>
+    <t>Transport.implicitRules</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -338,7 +338,7 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>Task.language</t>
+    <t>Transport.language</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -366,7 +366,7 @@
     <t>Resource.language</t>
   </si>
   <si>
-    <t>Task.text</t>
+    <t>Transport.text</t>
   </si>
   <si>
     <t>narrative
@@ -396,7 +396,7 @@
     <t>Act.text?</t>
   </si>
   <si>
-    <t>Task.contained</t>
+    <t>Transport.contained</t>
   </si>
   <si>
     <t>inline resources
@@ -426,7 +426,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Task.extension</t>
+    <t>Transport.extension</t>
   </si>
   <si>
     <t>extensions
@@ -453,7 +453,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Task.modifierExtension</t>
+    <t>Transport.modifierExtension</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -469,42 +469,42 @@
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
-    <t>Task.identifier</t>
+    <t>Transport.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Task Instance Identifier</t>
-  </si>
-  <si>
-    <t>The business identifier for this task.</t>
-  </si>
-  <si>
-    <t>Request.identifier, Event.identifier</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
+    <t>External identifier</t>
+  </si>
+  <si>
+    <t>Identifier for the transport event that is used to identify it across multiple disparate systems.</t>
+  </si>
+  <si>
+    <t>This identifier is typically assigned by the dispenser, and may be used to reference the delivery when exchanging information about it with other systems.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
   </si>
   <si>
     <t>.id</t>
   </si>
   <si>
-    <t>Task.instantiatesCanonical</t>
+    <t>Transport.instantiatesCanonical</t>
   </si>
   <si>
     <t xml:space="preserve">canonical(ActivityDefinition)
 </t>
   </si>
   <si>
-    <t>Formal definition of task</t>
-  </si>
-  <si>
-    <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
-  </si>
-  <si>
-    <t>Enables a formal definition of how the task is to be performed, enabling automation.</t>
+    <t>Formal definition of transport</t>
+  </si>
+  <si>
+    <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Transport.</t>
+  </si>
+  <si>
+    <t>Enables a formal definition of how the transport is to be performed, enabling automation.</t>
   </si>
   <si>
     <t>Request.instantiatesCanonical, Event.instantiatesCanonical</t>
@@ -513,32 +513,29 @@
     <t>.outboundRelationship[typeCode=DEFN].target</t>
   </si>
   <si>
-    <t>Task.instantiatesUri</t>
-  </si>
-  <si>
-    <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
-  </si>
-  <si>
-    <t>Enables a formal definition of how the task is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a task), enabling automation.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Task.basedOn</t>
+    <t>Transport.instantiatesUri</t>
+  </si>
+  <si>
+    <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Transport.</t>
+  </si>
+  <si>
+    <t>Enables a formal definition of how the transport is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a transport), enabling automation.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesUrl</t>
+  </si>
+  <si>
+    <t>Transport.basedOn</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
-    <t>Request fulfilled by this task</t>
-  </si>
-  <si>
-    <t>BasedOn refers to a higher-level authorization that triggered the creation of the task.  It references a "request" resource such as a ServiceRequest, MedicationRequest, CarePlan, etc. which is distinct from the "request" resource the task is seeking to fulfill.  This latter resource is referenced by focus.  For example, based on a CarePlan (= basedOn), a task is created to fulfill a ServiceRequest ( = focus ) to collect a specimen from a patient.</t>
-  </si>
-  <si>
-    <t>Task.basedOn is never the same as Task.focus.  Task.basedOn will typically not be present for 'please fulfill' Tasks as a distinct authorization is rarely needed to request fulfillment.  If the Task is seeking fulfillment of an order, the order to be fulfilled is always communicated using `focus`, never basedOn.  However, authorization may be needed to perform other types of Task actions.  As an example of when both would be present, a Task seeking suspension of a prescription might have a Task.basedOn pointing to the ServiceRequest ordering surgery (which is the driver for suspending the MedicationRequest - which would be the Task.focus).</t>
+    <t>Request fulfilled by this transport</t>
+  </si>
+  <si>
+    <t>BasedOn refers to a higher-level authorization that triggered the creation of the transport.  It references a "request" resource such as a ServiceRequest or Transport, which is distinct from the "request" resource the Transport is seeking to fulfill.  This latter resource is referenced by FocusOn.  For example, based on a ServiceRequest (= BasedOn), a transport is created to fulfill a procedureRequest ( = FocusOn ) to transport a specimen to the lab.</t>
   </si>
   <si>
     <t>Request.basedOn, Event.basedOn</t>
@@ -547,13 +544,13 @@
     <t>.outboundRelationship[typeCode=FLFS].target[moodCode=INT]</t>
   </si>
   <si>
-    <t>Task.groupIdentifier</t>
+    <t>Transport.groupIdentifier</t>
   </si>
   <si>
     <t>Requisition or grouper id</t>
   </si>
   <si>
-    <t>A shared identifier common to multiple independent Task and Request instances that were activated/authorized more or less simultaneously by a single author.  The presence of the same identifier on each request ties those requests together and may have business ramifications in terms of reporting of results, billing, etc.  E.g. a requisition number shared by a set of lab tests ordered together, or a prescription number shared by all meds ordered at one time.</t>
+    <t>A shared identifier common to multiple independent Request instances that were activated/authorized more or less simultaneously by a single author.  The presence of the same identifier on each request ties those requests together and may have business ramifications in terms of reporting of results, billing, etc.  E.g. a requisition number shared by a set of lab tests ordered together, or a prescription number shared by all meds ordered at one time.</t>
   </si>
   <si>
     <t>Billing and/or reporting can be linked to whether multiple requests were created as a single unit.</t>
@@ -565,122 +562,102 @@
     <t>.inboundRelationship[typeCode=COMP].source[moodCode=INT].id</t>
   </si>
   <si>
-    <t>Task.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Task)
+    <t>Transport.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Transport)
 </t>
   </si>
   <si>
-    <t>Composite task</t>
-  </si>
-  <si>
-    <t>Task that this particular task is part of.</t>
-  </si>
-  <si>
-    <t>This should usually be 0..1.</t>
-  </si>
-  <si>
-    <t>Allows tasks to be broken down into sub-steps (and this division can occur independent of the original task).</t>
+    <t>Part of referenced event</t>
+  </si>
+  <si>
+    <t>A larger event of which this particular event is a component or step.</t>
+  </si>
+  <si>
+    <t>Not to be used to link an event to an Encounter - use Event.context for that.++[The allowed reference resources may be adjusted as appropriate for the event resource].</t>
+  </si>
+  <si>
+    <t>E.g. Drug administration as part of a procedure, procedure as part of observation, etc.</t>
   </si>
   <si>
     <t>Event.partOf</t>
   </si>
   <si>
-    <t>.inboundRelationship[typeCode=COMP].source[moodCode=INT]</t>
-  </si>
-  <si>
-    <t>Task.status</t>
-  </si>
-  <si>
-    <t>draft | requested | received | accepted | +</t>
-  </si>
-  <si>
-    <t>The current status of the task.</t>
-  </si>
-  <si>
-    <t>These states enable coordination of task status with off-the-shelf workflow solutions that support automation of tasks.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/task-status|5.0.0</t>
-  </si>
-  <si>
-    <t>Request.status, Event.status</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>Task.statusReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableReference
-</t>
-  </si>
-  <si>
-    <t>Reason for current status</t>
-  </si>
-  <si>
-    <t>An explanation as to why this task is held, failed, was refused, etc.</t>
-  </si>
-  <si>
-    <t>This applies to the current status.  Look at the history of the task to see reasons for past statuses.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes to identify the reason for current status.  These will typically be specific to a particular workflow.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/task-status-reason</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
-  </si>
-  <si>
-    <t>Task.businessStatus</t>
+    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Varies by domain</t>
+  </si>
+  <si>
+    <t>Transport.status</t>
+  </si>
+  <si>
+    <t>in-progress | completed | abandoned | cancelled | planned | entered-in-error</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the transport event.</t>
+  </si>
+  <si>
+    <t>Status of the transport.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/transport-status|5.0.0</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>.statusCode, also existence of fulfillment events</t>
+  </si>
+  <si>
+    <t>Transport.statusReason</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>E.g. "Specimen collected", "IV prepped"</t>
-  </si>
-  <si>
-    <t>Contains business-specific nuances of the business state.</t>
-  </si>
-  <si>
-    <t>There's often a need to track substates of a task - this is often variable by specific workflow implementation.</t>
-  </si>
-  <si>
-    <t>The domain-specific business-contextual sub-state of the task.  For example: "Blood drawn", "IV inserted", "Awaiting physician signature", etc.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="business status"]</t>
-  </si>
-  <si>
-    <t>Task.intent</t>
+    <t>Reason for current status</t>
+  </si>
+  <si>
+    <t>An explanation as to why this transport is held, failed, was refused, etc.</t>
+  </si>
+  <si>
+    <t>This applies to the current status.  Look at the history of the transport to see reasons for past statuses.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes to identify the reason for current status.  These will typically be specific to a particular workflow.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/transport-status-reason</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
+  </si>
+  <si>
+    <t>Transport.intent</t>
   </si>
   <si>
     <t>unknown | proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
   </si>
   <si>
-    <t>Indicates the "level" of actionability associated with the Task, i.e. i+R[9]Cs this a proposed task, a planned task, an actionable task, etc.</t>
-  </si>
-  <si>
-    <t>This element is immutable.  Proposed tasks, planned tasks, etc. must be distinct instances.
-In most cases, Tasks will have an intent of "order".</t>
-  </si>
-  <si>
-    <t>Distinguishes whether the task is a proposal, plan or full order.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/task-intent|5.0.0</t>
+    <t>Indicates the "level" of actionability associated with the Transport, i.e. i+R[9]Cs this a proposed transport, a planned transport, an actionable transport, etc.</t>
+  </si>
+  <si>
+    <t>This element is immutable.  Proposed transports, planned transports, etc. must be distinct instances.
+In most cases, Transports will have an intent of "order".</t>
+  </si>
+  <si>
+    <t>Distinguishes whether the transport is a proposal, plan or full order.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/transport-intent|5.0.0</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -692,22 +669,22 @@
     <t>.moodCode</t>
   </si>
   <si>
-    <t>Task.priority</t>
+    <t>Transport.priority</t>
   </si>
   <si>
     <t>routine | urgent | asap | stat</t>
   </si>
   <si>
-    <t>Indicates how quickly the Task should be addressed with respect to other requests.</t>
-  </si>
-  <si>
-    <t>Used to identify the service level expected while performing a task.</t>
-  </si>
-  <si>
-    <t>If missing, this task should be performed with normal priority</t>
-  </si>
-  <si>
-    <t>The priority of a task (may affect service level applied to the task).</t>
+    <t>Indicates how quickly the Transport should be addressed with respect to other requests.</t>
+  </si>
+  <si>
+    <t>Used to identify the service level expected while performing a transport.</t>
+  </si>
+  <si>
+    <t>If missing, this transport should be performed with normal priority</t>
+  </si>
+  <si>
+    <t>The priority of a transport (may affect service level applied to the transport).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-priority|5.0.0</t>
@@ -722,22 +699,22 @@
     <t>.priorityCode</t>
   </si>
   <si>
-    <t>Task.doNotPerform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>True if Task is prohibiting action</t>
-  </si>
-  <si>
-    <t>If true indicates that the Task is asking for the specified action to *not* occur.</t>
-  </si>
-  <si>
-    <t>The attributes provided with the Task qualify what is not to be done. For example, if a requestedPeriod is provided, the 'do not' request only applies within the specified time. If a requestedPerformer is specified then the 'do not' request only applies to performers of that type. Qualifiers include: code, subject, occurrence, requestedPerformer and performer.
-In some cases, the Request.code may pre-coordinate prohibition into the requested action. E.g. 'NPO' (nothing by mouth), 'DNR' (do not recussitate). If this happens, doNotPerform SHALL NOT be set to true. I.e. The resource shall not have double negation. (E.g. 'Do not DNR').
-doNotPerform should ONLY be used with Tasks that are tightly bounded in time or process phase.  E.g. 'Do not fulfill the midnight dose of medication X tonight due to the early morning scheduled procedure, where the nurse could reasonably check off 'Med X not given at midnight as instructed'.  Similarly, a decision support proposal that a patient should not be given a standard intake questionnaire (because the patient is cognitively impaired) would be marked as 'complete' or 'rejected' when the clinician preps the CarePlan or order set after reviewing the decision support results.  If there is a need to create a standing order to not do something that can't be satisfied by a single 'non-action', but rather an ongoing refusal to perform the function, MedicationRequest, ServiceRequest or some other form of authorization should be used.</t>
+    <t>Transport.code</t>
+  </si>
+  <si>
+    <t>Transport Type</t>
+  </si>
+  <si>
+    <t>A name or code (or both) briefly describing what the transport involves.</t>
+  </si>
+  <si>
+    <t>The title (eg "My Transports", "Outstanding Transports for Patient X") should go into the code.</t>
+  </si>
+  <si>
+    <t>Codes to identify what the transport involves.  These will typically be specific to a particular workflow.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/transport-code</t>
   </si>
   <si>
     <t>Request.code, Event.code</t>
@@ -749,36 +726,14 @@
     <t>.code</t>
   </si>
   <si>
-    <t>Task.code</t>
-  </si>
-  <si>
-    <t>Task Type</t>
-  </si>
-  <si>
-    <t>A name or code (or both) briefly describing what the task involves.</t>
-  </si>
-  <si>
-    <t>The title (eg "My Tasks", "Outstanding Tasks for Patient X") should go into the code.</t>
-  </si>
-  <si>
-    <t>Codes to identify what the task involves.  These will typically be specific to a particular workflow.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/task-code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tsk-1
-</t>
-  </si>
-  <si>
-    <t>Task.description</t>
+    <t>Transport.description</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Human-readable explanation of task</t>
+    <t>Human-readable explanation of transport</t>
   </si>
   <si>
     <t>A free-text description of what is to be performed.</t>
@@ -787,16 +742,16 @@
     <t>.text</t>
   </si>
   <si>
-    <t>Task.focus</t>
-  </si>
-  <si>
-    <t>What task is acting on</t>
-  </si>
-  <si>
-    <t>The request being fulfilled or the resource being manipulated (changed, suspended, etc.) by this task.</t>
-  </si>
-  <si>
-    <t>If multiple resources need to be manipulated, use sub-tasks.  (This ensures that status can be tracked independently for each referenced resource.).</t>
+    <t>Transport.focus</t>
+  </si>
+  <si>
+    <t>What transport is acting on</t>
+  </si>
+  <si>
+    <t>The request being actioned or the resource being manipulated by this transport.</t>
+  </si>
+  <si>
+    <t>If multiple resources need to be manipulated, use sub-transports.  (This ensures that status can be tracked independently for each referenced resource.).</t>
   </si>
   <si>
     <t>Used to identify the thing to be done.</t>
@@ -805,20 +760,20 @@
     <t>.outboundRelationship[typeCode=SUBJ].target</t>
   </si>
   <si>
-    <t>Task.for</t>
+    <t>Transport.for</t>
   </si>
   <si>
     <t xml:space="preserve">Patient
 </t>
   </si>
   <si>
-    <t>Beneficiary of the Task</t>
-  </si>
-  <si>
-    <t>The entity who benefits from the performance of the service specified in the task (e.g., the patient).</t>
-  </si>
-  <si>
-    <t>Used to track tasks outstanding for a beneficiary.  Do not use to track the task owner or creator (see owner and creator respectively).  This can also affect access control.</t>
+    <t>Beneficiary of the Transport</t>
+  </si>
+  <si>
+    <t>The entity who benefits from the performance of the service specified in the transport (e.g., the patient).</t>
+  </si>
+  <si>
+    <t>Used to track transports outstanding for a beneficiary.  Do not use to track the transport owner or creator (see owner and creator respectively).  This can also affect access control.</t>
   </si>
   <si>
     <t>Request.subject, Event.subject</t>
@@ -830,20 +785,20 @@
     <t>.participation[typeCode=RCT].role</t>
   </si>
   <si>
-    <t>Task.encounter</t>
+    <t>Transport.encounter</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this task originated</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this task was created.</t>
-  </si>
-  <si>
-    <t>For some tasks it may be important to know the link between the encounter the task originated within.</t>
+    <t>Healthcare event during which this transport originated</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this transport was created.</t>
+  </si>
+  <si>
+    <t>For some transports it may be important to know the link between the encounter the transport originated within.</t>
   </si>
   <si>
     <t>Request.encounter, Event.encounter</t>
@@ -855,438 +810,342 @@
     <t>.inboundRelationship[typeCode=COMP].source[classCode=PCPR, moodCode=EVN]</t>
   </si>
   <si>
-    <t>Task.requestedPeriod</t>
+    <t>Transport.completionTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Completion time of the event (the occurrence)</t>
+  </si>
+  <si>
+    <t>Identifies the completion time of the event (the occurrence).</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>Transport.authoredOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created Date
+</t>
+  </si>
+  <si>
+    <t>Transport Creation Date</t>
+  </si>
+  <si>
+    <t>The date and time this transport was created.</t>
+  </si>
+  <si>
+    <t>Most often used along with lastUpdated to track duration of the transport to supporting monitoring and management.</t>
+  </si>
+  <si>
+    <t>Request.authoredOn</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>Transport.lastModified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update Date
+</t>
+  </si>
+  <si>
+    <t>Transport Last Modified Date</t>
+  </si>
+  <si>
+    <t>The date and time of last modification to this transport.</t>
+  </si>
+  <si>
+    <t>Used along with history to track transport activity and time in a particular transport state.  This enables monitoring and management.</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ, ].source[classCode=CACT, moodCode=EVN].effectiveTime</t>
+  </si>
+  <si>
+    <t>Transport.requester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Who is asking for transport to be done</t>
+  </si>
+  <si>
+    <t>The creator of the transport.</t>
+  </si>
+  <si>
+    <t>Identifies who created this transport.  May be used by access control mechanisms (e.g., to ensure that only the creator can cancel a transport).</t>
+  </si>
+  <si>
+    <t>Request.requester</t>
+  </si>
+  <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>Transport.performerType</t>
+  </si>
+  <si>
+    <t>Requested performer</t>
+  </si>
+  <si>
+    <t>The kind of participant that should perform the transport.</t>
+  </si>
+  <si>
+    <t>Use to distinguish transports on different activity queues.</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>The type(s) of transport performers allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+  </si>
+  <si>
+    <t>Event.performer.function, Request.performerType</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF].role.code</t>
+  </si>
+  <si>
+    <t>Transport.owner</t>
+  </si>
+  <si>
+    <t>Performer
+Executer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Responsible individual</t>
+  </si>
+  <si>
+    <t>Individual organization or Device currently responsible for transport execution.</t>
+  </si>
+  <si>
+    <t>Transports may be created with an owner not yet identified.</t>
+  </si>
+  <si>
+    <t>Identifies who is expected to perform this transport.</t>
+  </si>
+  <si>
+    <t>Event.performer.actor, Request.performer</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF].role</t>
+  </si>
+  <si>
+    <t>Transport.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
+  </si>
+  <si>
+    <t>Where transport occurs</t>
+  </si>
+  <si>
+    <t>Principal physical location where this transport is performed.</t>
+  </si>
+  <si>
+    <t>Ties the event to where the records are likely kept and provides context around the event occurrence (e.g. if it occurred inside or outside a dedicated healthcare setting).</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=LOC].role</t>
+  </si>
+  <si>
+    <t>Transport.insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+</t>
+  </si>
+  <si>
+    <t>Associated insurance coverage</t>
+  </si>
+  <si>
+    <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be relevant to the Transport.</t>
+  </si>
+  <si>
+    <t>Request.insurance</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COVBY].target</t>
+  </si>
+  <si>
+    <t>IN1/IN2</t>
+  </si>
+  <si>
+    <t>Transport.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Comments made about the transport</t>
+  </si>
+  <si>
+    <t>Free-text information captured about the transport as it progresses.</t>
+  </si>
+  <si>
+    <t>Request.note, Event.note</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ, ].source[classCode=OBS, moodCode=EVN, code="annotation"].value(string)</t>
+  </si>
+  <si>
+    <t>Transport.relevantHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status History
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Provenance)
+</t>
+  </si>
+  <si>
+    <t>Key events in history of the Transport</t>
+  </si>
+  <si>
+    <t>Links to Provenance records for past versions of this Transport that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the transport.</t>
+  </si>
+  <si>
+    <t>This element does not point to the Provenance associated with the *current* version of the resource - as it would be created after this version existed.  The Provenance for the current version can be retrieved with a _revinclude.</t>
+  </si>
+  <si>
+    <t>Request.relevantHistory</t>
+  </si>
+  <si>
+    <t>.inboundRelationship(typeCode=SUBJ].source[classCode=CACT, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Transport.restriction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Constraints on fulfillment transports</t>
+  </si>
+  <si>
+    <t>If the Transport.focus is a request resource and the transport is seeking fulfillment (i.e. is asking for the request to be actioned), this element identifies any limitations on what parts of the referenced request should be actioned.</t>
+  </si>
+  <si>
+    <t>Sometimes when fulfillment is sought, you don't want full fulfillment.</t>
+  </si>
+  <si>
+    <t>Instead of pointing to request, would point to component of request, having these characteristics</t>
+  </si>
+  <si>
+    <t>Transport.restriction.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Transport.restriction.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Transport.restriction.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Transport.restriction.repetitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positiveInt
+</t>
+  </si>
+  <si>
+    <t>How many times to repeat</t>
+  </si>
+  <si>
+    <t>Indicates the number of times the requested action should occur.</t>
+  </si>
+  <si>
+    <t>E.g. order that requests monthly lab tests, fulfillment is sought for 1.</t>
+  </si>
+  <si>
+    <t>.repeatNumber</t>
+  </si>
+  <si>
+    <t>Transport.restriction.period</t>
   </si>
   <si>
     <t xml:space="preserve">Period
 </t>
   </si>
   <si>
-    <t>When the task should be performed</t>
-  </si>
-  <si>
-    <t>Indicates the start and/or end of the period of time when completion of the task is desired to take place.</t>
-  </si>
-  <si>
-    <t>This is typically used when the Task is *not* seeking fulfillment of a focus Request, as in that case the period would be specified on the Request and/or in the Task.restriction.period.  Instead, it is used for stand-alone tasks.</t>
-  </si>
-  <si>
-    <t>Request.occurrence[x]</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>Task.executionPeriod</t>
-  </si>
-  <si>
-    <t>Start and end time of execution</t>
-  </si>
-  <si>
-    <t>Identifies the time action was first taken against the task (start) and/or the time final action was taken against the task prior to marking it as completed (end).</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Task.authoredOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Created Date
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Task Creation Date</t>
-  </si>
-  <si>
-    <t>The date and time this task was created.</t>
-  </si>
-  <si>
-    <t>Most often used along with lastUpdated to track duration of task to supporting monitoring and management.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Request.authoredOn</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>Task.lastModified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Update Date
-</t>
-  </si>
-  <si>
-    <t>Task Last Modified Date</t>
-  </si>
-  <si>
-    <t>The date and time of last modification to this task.</t>
-  </si>
-  <si>
-    <t>Used along with history to track task activity and time in a particular task state.  This enables monitoring and management.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ, ].source[classCode=CACT, moodCode=EVN].effectiveTime</t>
-  </si>
-  <si>
-    <t>Task.requester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Who is asking for task to be done</t>
-  </si>
-  <si>
-    <t>The creator of the task.</t>
-  </si>
-  <si>
-    <t>Identifies who created this task.  May be used by access control mechanisms (e.g., to ensure that only the creator can cancel a task).</t>
-  </si>
-  <si>
-    <t>Request.requester</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>Task.requestedPerformer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableReference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Who should perform Task</t>
-  </si>
-  <si>
-    <t>The kind of participant or specific participant that should perform the task.</t>
-  </si>
-  <si>
-    <t>Use to distinguish tasks on different activity queues.</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>The type(s) of task performers allowed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
-  </si>
-  <si>
-    <t>Event.performer.function, Request.performerType</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF].role.code</t>
-  </si>
-  <si>
-    <t>Task.owner</t>
-  </si>
-  <si>
-    <t>Performer
-Executer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Responsible individual</t>
-  </si>
-  <si>
-    <t>Party responsible for managing task execution.</t>
-  </si>
-  <si>
-    <t>Tasks may be created with an owner not yet identified.</t>
-  </si>
-  <si>
-    <t>Identifies who is expected to perform this task.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor, Request.performer</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF].role</t>
-  </si>
-  <si>
-    <t>Task.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Who or what performed the task</t>
-  </si>
-  <si>
-    <t>The entity who performed the requested task.</t>
-  </si>
-  <si>
-    <t>Task.performer.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Task.performer.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Task.performer.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Task.performer.function</t>
-  </si>
-  <si>
-    <t>Type of performance</t>
-  </si>
-  <si>
-    <t>A code or description of the performer of the task.</t>
-  </si>
-  <si>
-    <t>Codes to identify types of task performers.</t>
-  </si>
-  <si>
-    <t>Task.performer.actor</t>
-  </si>
-  <si>
-    <t>Who performed the task</t>
-  </si>
-  <si>
-    <t>The actor or entity who performed the task.</t>
-  </si>
-  <si>
-    <t>Task.location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location)
-</t>
-  </si>
-  <si>
-    <t>Where task occurs</t>
-  </si>
-  <si>
-    <t>Principal physical location where this task is performed.</t>
-  </si>
-  <si>
-    <t>This should only be specified when the Task to be/being performed happens or is expected to happen primarily within the bounds of a single Location.  Other locations (e.g. source, destination, etc.) would either be reflected on the 'basedOn' Request or be conveyed as distinct Task.input values.</t>
-  </si>
-  <si>
-    <t>Ties the event to where the records are likely kept and provides context around the event occurrence (e.g. if it occurred inside or outside a dedicated healthcare setting).</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=LOC].role</t>
-  </si>
-  <si>
-    <t>Task.reason</t>
-  </si>
-  <si>
-    <t>Why task is needed</t>
-  </si>
-  <si>
-    <t>A description, code, or reference indicating why this task needs to be performed.</t>
-  </si>
-  <si>
-    <t>This will typically not be present for Tasks with a code of 'please fulfill' as, for those, the reason for action is conveyed on the Request pointed to by Task.focus.  Some types of tasks will not need a 'reason'.  E.g. a request to discharge a patient can be inferred to be 'because the patient is ready' and this would not need a reason to be stated on the Task.</t>
-  </si>
-  <si>
-    <t>Indicates why the task is needed.  E.g. Suspended because patient admitted to hospital.</t>
-  </si>
-  <si>
-    <t>Event.reason, Request.reason</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>EVN.7</t>
-  </si>
-  <si>
-    <t>Task.insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
-</t>
-  </si>
-  <si>
-    <t>Associated insurance coverage</t>
-  </si>
-  <si>
-    <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be relevant to the Task.</t>
-  </si>
-  <si>
-    <t>Request.insurance</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COVBY].target</t>
-  </si>
-  <si>
-    <t>IN1/IN2</t>
-  </si>
-  <si>
-    <t>Task.note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Comments made about the task</t>
-  </si>
-  <si>
-    <t>Free-text information captured about the task as it progresses.</t>
-  </si>
-  <si>
-    <t>Request.note, Event.note</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ, ].source[classCode=OBS, moodCode=EVN, code="annotation"].value(string)</t>
-  </si>
-  <si>
-    <t>Task.relevantHistory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status History
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Provenance)
-</t>
-  </si>
-  <si>
-    <t>Key events in history of the Task</t>
-  </si>
-  <si>
-    <t>Links to Provenance records for past versions of this Task that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the task.</t>
-  </si>
-  <si>
-    <t>This element does not point to the Provenance associated with the *current* version of the resource - as it would be created after this version existed.  The Provenance for the current version can be retrieved with a _revinclude.</t>
-  </si>
-  <si>
-    <t>Request.relevantHistory</t>
-  </si>
-  <si>
-    <t>.inboundRelationship(typeCode=SUBJ].source[classCode=CACT, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Task.restriction</t>
-  </si>
-  <si>
-    <t>Constraints on fulfillment tasks</t>
-  </si>
-  <si>
-    <t>If the Task.focus is a request resource and the task is seeking fulfillment (i.e. is asking for the request to be actioned), this element identifies any limitations on what parts of the referenced request should be actioned.</t>
-  </si>
-  <si>
-    <t>Task.restriction can only be present if the Task is seeking fulfillment of another Request resource, and the restriction identifies what subset of the authorization conveyed by the request is supposed to be fulfilled by this Task. A possible example could be a standing order (the request) covering a significant time period and/or individuals, while the Task seeks fulfillment for only a subset of that time-period and a single individual.</t>
-  </si>
-  <si>
-    <t>Sometimes when fulfillment is sought, you don't want full fulfillment.</t>
-  </si>
-  <si>
-    <t>Instead of pointing to request, would point to component of request, having these characteristics</t>
-  </si>
-  <si>
-    <t>Task.restriction.id</t>
-  </si>
-  <si>
-    <t>Task.restriction.extension</t>
-  </si>
-  <si>
-    <t>Task.restriction.modifierExtension</t>
-  </si>
-  <si>
-    <t>Task.restriction.repetitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positiveInt
-</t>
-  </si>
-  <si>
-    <t>How many times to repeat</t>
-  </si>
-  <si>
-    <t>Indicates the number of times the requested action should occur.</t>
-  </si>
-  <si>
-    <t>E.g. order that requests monthly lab tests, fulfillment is sought for 1.</t>
-  </si>
-  <si>
-    <t>.repeatNumber</t>
-  </si>
-  <si>
-    <t>Task.restriction.period</t>
-  </si>
-  <si>
-    <t>When fulfillment is sought</t>
-  </si>
-  <si>
-    <t>The time-period for which fulfillment is sought. This must fall within the overall time period authorized in the referenced request.  E.g. ServiceRequest.occurance[x].</t>
-  </si>
-  <si>
-    <t>This is distinct from Task.executionPeriod. ExecutionPeriod indicates when the task needs to be initiated, while Task.restriction.period specifies the subset of the overall authorization that this period covers. For example, a MedicationRequest with an overall effective period of 1 year might have a Task whose restriction.period is 2 months (i.e. satisfy 2 months of medication therapy), while the execution period might be 'between now and 5 days from now' - i.e. If you say yes to this, then you're agreeing to supply medication for that 2 month period within the next 5 days.
-Note that period.high is the due date representing the time by which the task should be completed.</t>
+    <t>When fulfillment sought</t>
+  </si>
+  <si>
+    <t>Over what time-period is fulfillment sought.</t>
+  </si>
+  <si>
+    <t>Note that period.high is the due date representing the time by which the transport should be completed.</t>
   </si>
   <si>
     <t>E.g. order that authorizes 1 year's services.  Fulfillment is sought for next 3 months.</t>
@@ -1295,7 +1154,7 @@
     <t>.effectiveTime(IVL&lt;TS&gt;)</t>
   </si>
   <si>
-    <t>Task.restriction.recipient</t>
+    <t>Transport.restriction.recipient</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Group|Organization)
@@ -1311,35 +1170,35 @@
     <t>.participation[typeCode=SBJ].role</t>
   </si>
   <si>
-    <t>Task.input</t>
+    <t>Transport.input</t>
   </si>
   <si>
     <t xml:space="preserve">Supporting Information
 </t>
   </si>
   <si>
-    <t>Information used to perform task</t>
-  </si>
-  <si>
-    <t>Additional information that may be needed in the execution of the task.</t>
-  </si>
-  <si>
-    <t>Resources and data used to perform the task.  This data is used in the business logic of task execution, and is stored separately because it varies between workflows.</t>
+    <t>Information used to perform transport</t>
+  </si>
+  <si>
+    <t>Additional information that may be needed in the execution of the transport.</t>
+  </si>
+  <si>
+    <t>Resources and data used to perform the transport.  This data is used in the business logic of transport execution, and is stored separately because it varies between workflows.</t>
   </si>
   <si>
     <t>???</t>
   </si>
   <si>
-    <t>Task.input.id</t>
-  </si>
-  <si>
-    <t>Task.input.extension</t>
-  </si>
-  <si>
-    <t>Task.input.modifierExtension</t>
-  </si>
-  <si>
-    <t>Task.input.type</t>
+    <t>Transport.input.id</t>
+  </si>
+  <si>
+    <t>Transport.input.extension</t>
+  </si>
+  <si>
+    <t>Transport.input.modifierExtension</t>
+  </si>
+  <si>
+    <t>Transport.input.type</t>
   </si>
   <si>
     <t xml:space="preserve">Name
@@ -1349,53 +1208,53 @@
     <t>Label for the input</t>
   </si>
   <si>
-    <t>A code or description indicating how the input is intended to be used as part of the task execution.</t>
+    <t>A code or description indicating how the input is intended to be used as part of the transport execution.</t>
   </si>
   <si>
     <t>If referencing a BPMN workflow or Protocol, the "system" is the URL for the workflow definition and the code is the "name" of the required input.</t>
   </si>
   <si>
-    <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
+    <t>Inputs are named to enable transport automation to bind data and pass it from one transport to the next.</t>
   </si>
   <si>
     <t>Codes to identify types of input parameters.  These will typically be specific to a particular workflow.  E.g. "Comparison source", "Applicable consent", "Concomitent Medications", etc.</t>
   </si>
   <si>
-    <t>Task.input.value[x]</t>
+    <t>Transport.input.value[x]</t>
   </si>
   <si>
     <t>base64Binary
 booleancanonicalcodedatedateTimedecimalidinstantintegerinteger64markdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodeableReferenceCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioRatioRangeReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextAvailabilityExtendedContactDetailDosageMeta</t>
   </si>
   <si>
-    <t>Content to use in performing the task</t>
+    <t>Content to use in performing the transport</t>
   </si>
   <si>
     <t>The value of the input parameter as a basic type.</t>
   </si>
   <si>
-    <t>Task.output</t>
-  </si>
-  <si>
-    <t>Information produced as part of task</t>
-  </si>
-  <si>
-    <t>Outputs produced by the Task.</t>
-  </si>
-  <si>
-    <t>Resources and data produced during the execution the task.  This data is generated by the business logic of task execution, and is stored separately because it varies between workflows.</t>
-  </si>
-  <si>
-    <t>Task.output.id</t>
-  </si>
-  <si>
-    <t>Task.output.extension</t>
-  </si>
-  <si>
-    <t>Task.output.modifierExtension</t>
-  </si>
-  <si>
-    <t>Task.output.type</t>
+    <t>Transport.output</t>
+  </si>
+  <si>
+    <t>Information produced as part of transport</t>
+  </si>
+  <si>
+    <t>Outputs produced by the Transport.</t>
+  </si>
+  <si>
+    <t>Resources and data produced during the execution the transport.  This data is generated by the business logic of transport execution, and is stored separately because it varies between workflows.</t>
+  </si>
+  <si>
+    <t>Transport.output.id</t>
+  </si>
+  <si>
+    <t>Transport.output.extension</t>
+  </si>
+  <si>
+    <t>Transport.output.modifierExtension</t>
+  </si>
+  <si>
+    <t>Transport.output.type</t>
   </si>
   <si>
     <t>Label for output</t>
@@ -1404,13 +1263,13 @@
     <t>The name of the Output parameter.</t>
   </si>
   <si>
-    <t>Outputs are named to enable task automation to bind data and pass it from one task to the next.</t>
+    <t>Outputs are named to enable transport automation to bind data and pass it from one transport to the next.</t>
   </si>
   <si>
     <t>Codes to identify types of input parameters.  These will typically be specific to a particular workflow.  E.g. "Identified issues", "Preliminary results", "Filler order", "Final results", etc.</t>
   </si>
   <si>
-    <t>Task.output.value[x]</t>
+    <t>Transport.output.value[x]</t>
   </si>
   <si>
     <t>Result of output</t>
@@ -1419,7 +1278,62 @@
     <t>The value of the Output parameter as a basic type.</t>
   </si>
   <si>
-    <t>Task outputs can take any form.</t>
+    <t>Transport outputs can take any form.</t>
+  </si>
+  <si>
+    <t>Transport.requestedLocation</t>
+  </si>
+  <si>
+    <t>The desired location</t>
+  </si>
+  <si>
+    <t>The desired or final location for the transport.</t>
+  </si>
+  <si>
+    <t>Transport.currentLocation</t>
+  </si>
+  <si>
+    <t>The entity current location</t>
+  </si>
+  <si>
+    <t>The current location for the entity to be transported.</t>
+  </si>
+  <si>
+    <t>Transport.reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference(Resource)
+</t>
+  </si>
+  <si>
+    <t>Why transport is needed</t>
+  </si>
+  <si>
+    <t>A resource reference indicating why this transport needs to be performed.</t>
+  </si>
+  <si>
+    <t>Transports might be justified based on an Observation, a Condition, a past or planned procedure, etc. This should only be included if there is no focus or if it differs from the reason indicated on the focus.    Use the CodeableConcept text element in `Transport.reasonCode` if the data is free (uncoded) text.</t>
+  </si>
+  <si>
+    <t>Indicates why the transport is needed.  E.g. Suspended because patient admitted to hospital.</t>
+  </si>
+  <si>
+    <t>Request.reason, Event.reason</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RSON].target</t>
+  </si>
+  <si>
+    <t>Transport.history</t>
+  </si>
+  <si>
+    <t>Parent (or preceding) transport</t>
+  </si>
+  <si>
+    <t>The transport event prior to this one.</t>
   </si>
 </sst>
 </file>
@@ -1744,11 +1658,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN64"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.42578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.0390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.0390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -1772,7 +1686,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.90234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -2970,7 +2884,9 @@
       <c r="M11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -3034,10 +2950,10 @@
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>151</v>
@@ -3310,9 +3226,7 @@
       <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -3376,13 +3290,13 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>76</v>
@@ -3390,10 +3304,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3419,14 +3333,14 @@
         <v>146</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3475,7 +3389,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3490,13 +3404,13 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>76</v>
@@ -3504,10 +3418,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3530,19 +3444,19 @@
         <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3591,7 +3505,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3606,16 +3520,16 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AL16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -3655,9 +3569,7 @@
         <v>186</v>
       </c>
       <c r="N17" s="2"/>
-      <c r="O17" t="s" s="2">
-        <v>187</v>
-      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>76</v>
       </c>
@@ -3684,7 +3596,7 @@
         <v>110</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>188</v>
@@ -3708,7 +3620,7 @@
         <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>86</v>
@@ -3723,10 +3635,10 @@
         <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>76</v>
@@ -3734,10 +3646,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3760,16 +3672,16 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3795,14 +3707,14 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>199</v>
-      </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
       </c>
@@ -3819,7 +3731,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3840,7 +3752,7 @@
         <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>76</v>
@@ -3848,10 +3760,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3859,7 +3771,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>86</v>
@@ -3874,18 +3786,18 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>76</v>
       </c>
@@ -3909,13 +3821,13 @@
         <v>76</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>76</v>
+        <v>205</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>76</v>
@@ -3933,10 +3845,10 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>86</v>
@@ -3948,13 +3860,13 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>76</v>
@@ -3962,10 +3874,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3973,7 +3885,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>86</v>
@@ -3985,25 +3897,27 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="O20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q20" s="2"/>
+      <c r="Q20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="R20" t="s" s="2">
         <v>76</v>
       </c>
@@ -4026,10 +3940,10 @@
         <v>110</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>76</v>
@@ -4047,10 +3961,10 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>86</v>
@@ -4062,13 +3976,13 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>76</v>
@@ -4076,10 +3990,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4099,71 +4013,69 @@
         <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="R21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4178,13 +4090,13 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
@@ -4192,10 +4104,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4212,23 +4124,21 @@
         <v>76</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N22" t="s" s="2">
         <v>231</v>
       </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -4277,7 +4187,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4292,13 +4202,13 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>76</v>
@@ -4306,10 +4216,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4332,18 +4242,20 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>76</v>
       </c>
@@ -4367,13 +4279,13 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>239</v>
+        <v>76</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>76</v>
@@ -4391,7 +4303,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4400,19 +4312,19 @@
         <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>232</v>
+        <v>76</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>76</v>
@@ -4420,14 +4332,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4446,16 +4358,18 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>76</v>
       </c>
@@ -4503,7 +4417,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4518,10 +4432,10 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>76</v>
+        <v>244</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>76</v>
+        <v>245</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>246</v>
@@ -4558,17 +4472,15 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>164</v>
+        <v>248</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N25" t="s" s="2">
         <v>250</v>
       </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>251</v>
       </c>
@@ -4628,19 +4540,19 @@
         <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>76</v>
@@ -4648,14 +4560,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>254</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4674,18 +4586,16 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
@@ -4733,7 +4643,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4748,13 +4658,13 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>76</v>
@@ -4762,18 +4672,18 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>86</v>
@@ -4785,20 +4695,20 @@
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4847,7 +4757,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4862,13 +4772,13 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
@@ -4876,14 +4786,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>76</v>
+        <v>271</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4902,18 +4812,18 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N28" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="O28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
       </c>
@@ -4961,7 +4871,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4976,7 +4886,7 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>274</v>
+        <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -5001,7 +4911,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>86</v>
@@ -5016,16 +4926,18 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
@@ -5088,13 +5000,13 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>76</v>
@@ -5102,21 +5014,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>282</v>
+        <v>76</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -5128,17 +5040,17 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>283</v>
+        <v>192</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -5163,13 +5075,13 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>76</v>
+        <v>288</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>76</v>
+        <v>289</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>76</v>
+        <v>290</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>76</v>
@@ -5187,28 +5099,28 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>287</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>76</v>
@@ -5216,14 +5128,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5242,17 +5154,19 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O31" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5301,7 +5215,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5310,19 +5224,19 @@
         <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>287</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>76</v>
+        <v>301</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>76</v>
+        <v>292</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>76</v>
@@ -5330,10 +5244,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5356,17 +5270,17 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5415,7 +5329,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5430,13 +5344,13 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>302</v>
+        <v>76</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>76</v>
@@ -5444,10 +5358,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5470,18 +5384,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>76</v>
       </c>
@@ -5505,31 +5417,31 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5544,44 +5456,44 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>314</v>
+        <v>76</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>76</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>317</v>
+        <v>76</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>318</v>
@@ -5592,12 +5504,8 @@
       <c r="M34" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
@@ -5645,13 +5553,13 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
@@ -5660,13 +5568,13 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>314</v>
+        <v>76</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>76</v>
@@ -5674,14 +5582,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>76</v>
+        <v>324</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5697,18 +5605,20 @@
         <v>76</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5757,7 +5667,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5772,13 +5682,13 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>76</v>
+        <v>329</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>76</v>
+        <v>330</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>76</v>
@@ -5786,10 +5696,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5812,16 +5722,18 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>76</v>
       </c>
@@ -5869,7 +5781,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5878,10 +5790,10 @@
         <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>333</v>
+        <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>76</v>
@@ -5890,7 +5802,7 @@
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>76</v>
@@ -5898,21 +5810,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -5924,17 +5836,15 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5983,19 +5893,19 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>76</v>
@@ -6004,7 +5914,7 @@
         <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>76</v>
@@ -6012,14 +5922,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>339</v>
+        <v>133</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6032,26 +5942,24 @@
         <v>76</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="O38" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
       </c>
@@ -6099,7 +6007,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6120,7 +6028,7 @@
         <v>76</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>131</v>
+        <v>342</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>76</v>
@@ -6128,42 +6036,46 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>76</v>
+        <v>347</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>76</v>
       </c>
@@ -6187,10 +6099,10 @@
         <v>76</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>346</v>
+        <v>76</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>76</v>
@@ -6211,19 +6123,19 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
@@ -6232,7 +6144,7 @@
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>76</v>
@@ -6240,10 +6152,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6251,7 +6163,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>86</v>
@@ -6263,19 +6175,21 @@
         <v>76</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>76</v>
       </c>
@@ -6323,10 +6237,10 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>86</v>
@@ -6344,7 +6258,7 @@
         <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>76</v>
+        <v>356</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>76</v>
@@ -6352,10 +6266,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6375,22 +6289,22 @@
         <v>76</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -6439,7 +6353,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6457,10 +6371,10 @@
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>356</v>
+        <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>76</v>
@@ -6468,10 +6382,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6494,17 +6408,15 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>193</v>
+        <v>365</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6529,10 +6441,10 @@
         <v>76</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>362</v>
+        <v>76</v>
       </c>
       <c r="Z42" t="s" s="2">
         <v>76</v>
@@ -6553,7 +6465,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6568,28 +6480,28 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>363</v>
+        <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>364</v>
+        <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>366</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>76</v>
+        <v>370</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6608,16 +6520,18 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
       </c>
@@ -6665,7 +6579,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6680,24 +6594,24 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>371</v>
+        <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>373</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6708,10 +6622,10 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>76</v>
@@ -6720,13 +6634,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>375</v>
+        <v>229</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>377</v>
+        <v>339</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6777,28 +6691,28 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>378</v>
+        <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>379</v>
+        <v>342</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>76</v>
@@ -6806,14 +6720,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>381</v>
+        <v>133</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6832,16 +6746,16 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>382</v>
+        <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>383</v>
+        <v>135</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>385</v>
+        <v>137</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6891,7 +6805,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6903,16 +6817,16 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>386</v>
+        <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>76</v>
@@ -6920,45 +6834,45 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>76</v>
+        <v>347</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>326</v>
+        <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>390</v>
+        <v>349</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>391</v>
+        <v>137</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>392</v>
+        <v>143</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -7007,19 +6921,19 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>388</v>
+        <v>350</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
@@ -7028,7 +6942,7 @@
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>393</v>
+        <v>131</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>76</v>
@@ -7036,18 +6950,18 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>86</v>
@@ -7062,16 +6976,20 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
       </c>
@@ -7095,10 +7013,10 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>76</v>
+        <v>384</v>
       </c>
       <c r="Z47" t="s" s="2">
         <v>76</v>
@@ -7119,19 +7037,19 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>333</v>
+        <v>76</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>76</v>
@@ -7140,7 +7058,7 @@
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>334</v>
+        <v>374</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>76</v>
@@ -7148,21 +7066,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>76</v>
@@ -7174,17 +7092,15 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>386</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>135</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7233,19 +7149,19 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>337</v>
+        <v>385</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>76</v>
@@ -7254,7 +7170,7 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>334</v>
+        <v>374</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>76</v>
@@ -7262,14 +7178,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>339</v>
+        <v>76</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7282,25 +7198,23 @@
         <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>134</v>
+        <v>332</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>143</v>
+        <v>392</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -7349,7 +7263,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>342</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7361,7 +7275,7 @@
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>76</v>
@@ -7370,7 +7284,7 @@
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>131</v>
+        <v>374</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>76</v>
@@ -7378,10 +7292,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7404,18 +7318,16 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>398</v>
+        <v>229</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>399</v>
+        <v>338</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>400</v>
+        <v>339</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>76</v>
       </c>
@@ -7463,7 +7375,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7472,10 +7384,10 @@
         <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>76</v>
@@ -7484,7 +7396,7 @@
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>402</v>
+        <v>342</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>76</v>
@@ -7492,21 +7404,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>76</v>
@@ -7518,20 +7430,18 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>270</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>404</v>
+        <v>135</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>405</v>
+        <v>344</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>76</v>
       </c>
@@ -7579,19 +7489,19 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>403</v>
+        <v>345</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>76</v>
@@ -7600,7 +7510,7 @@
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>76</v>
@@ -7608,14 +7518,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>76</v>
+        <v>347</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7628,22 +7538,26 @@
         <v>76</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>410</v>
+        <v>134</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>411</v>
+        <v>348</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
       </c>
@@ -7691,7 +7605,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>350</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7703,7 +7617,7 @@
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
@@ -7712,7 +7626,7 @@
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>413</v>
+        <v>131</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>76</v>
@@ -7720,21 +7634,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>76</v>
@@ -7746,17 +7660,17 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>326</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7781,10 +7695,10 @@
         <v>76</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>76</v>
@@ -7805,13 +7719,13 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>76</v>
@@ -7826,7 +7740,7 @@
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>76</v>
@@ -7834,10 +7748,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7845,7 +7759,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>86</v>
@@ -7860,16 +7774,18 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>243</v>
+        <v>386</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>330</v>
+        <v>402</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>331</v>
+        <v>403</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>76</v>
       </c>
@@ -7917,19 +7833,19 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>332</v>
+        <v>401</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>333</v>
+        <v>76</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>76</v>
@@ -7938,7 +7854,7 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>334</v>
+        <v>374</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>76</v>
@@ -7946,21 +7862,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>76</v>
@@ -7969,20 +7885,18 @@
         <v>76</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>135</v>
+        <v>406</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -8031,28 +7945,28 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>337</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>76</v>
+        <v>308</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>76</v>
@@ -8060,46 +7974,42 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>339</v>
+        <v>76</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>76</v>
       </c>
@@ -8147,28 +8057,28 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>342</v>
+        <v>408</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>76</v>
+        <v>308</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>131</v>
+        <v>309</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>76</v>
@@ -8176,18 +8086,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>424</v>
+        <v>76</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>86</v>
@@ -8202,20 +8112,18 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>202</v>
+        <v>412</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>76</v>
       </c>
@@ -8239,10 +8147,10 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="Z57" t="s" s="2">
         <v>76</v>
@@ -8263,10 +8171,10 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>86</v>
@@ -8278,10 +8186,10 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>76</v>
+        <v>417</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>76</v>
+        <v>418</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>419</v>
@@ -8292,10 +8200,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8303,7 +8211,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>86</v>
@@ -8318,13 +8226,13 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>431</v>
+        <v>176</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8375,10 +8283,10 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>86</v>
@@ -8393,7 +8301,7 @@
         <v>76</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>76</v>
+        <v>418</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>419</v>
@@ -8402,692 +8310,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN64">
+  <autoFilter ref="A1:AN58">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9097,7 +8321,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/result-dispatched-to-facility</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/result-dispatched-to-facility</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/result-dispatched-to-facility</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/result-dispatched-to-facility</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:13:26+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$57</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="383">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:20:07+00:00</t>
+    <t>2023-07-05T16:42:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,126 +124,6 @@
   </si>
   <si>
     <t>constraint</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Slice Name</t>
-  </si>
-  <si>
-    <t>Alias(s)</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Must Support?</t>
-  </si>
-  <si>
-    <t>Is Modifier?</t>
-  </si>
-  <si>
-    <t>Is Summary?</t>
-  </si>
-  <si>
-    <t>Type(s)</t>
-  </si>
-  <si>
-    <t>Short</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Requirements</t>
-  </si>
-  <si>
-    <t>Default Value</t>
-  </si>
-  <si>
-    <t>Meaning When Missing</t>
-  </si>
-  <si>
-    <t>Fixed Value</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>Minimum Value</t>
-  </si>
-  <si>
-    <t>Maximum Value</t>
-  </si>
-  <si>
-    <t>Maximum Length</t>
-  </si>
-  <si>
-    <t>Binding Strength</t>
-  </si>
-  <si>
-    <t>Binding Description</t>
-  </si>
-  <si>
-    <t>Binding Value Set</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Slicing Discriminator</t>
-  </si>
-  <si>
-    <t>Slicing Description</t>
-  </si>
-  <si>
-    <t>Slicing Ordered</t>
-  </si>
-  <si>
-    <t>Slicing Rules</t>
-  </si>
-  <si>
-    <t>Base Path</t>
-  </si>
-  <si>
-    <t>Base Min</t>
-  </si>
-  <si>
-    <t>Base Max</t>
-  </si>
-  <si>
-    <t>Condition(s)</t>
-  </si>
-  <si>
-    <t>Constraint(s)</t>
-  </si>
-  <si>
-    <t>Mapping: Workflow Pattern</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t/>
@@ -1455,10 +1335,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -1658,18 +1538,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN58"/>
+  <dimension ref="A1:AN57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.0390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.0390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="2.1640625" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1680,6638 +1558,6517 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="9.6640625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.1328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="47.90234375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="1.04296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="2.2109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" hidden="true" width="8.0" customWidth="false"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="55.72265625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="17.33203125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="109.98828125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="28.37109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="17.046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>37</v>
-      </c>
-      <c r="C1" t="s" s="1">
+      <c r="A1" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="H1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="I1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="L1" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="M1" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="2"/>
+      <c r="R1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="S1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF1" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="AG1" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AH1" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AI1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AJ1" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AK1" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="AL1" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="AM1" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="J1" t="s" s="1">
-        <v>45</v>
-      </c>
-      <c r="K1" t="s" s="1">
-        <v>46</v>
-      </c>
-      <c r="L1" t="s" s="1">
-        <v>47</v>
-      </c>
-      <c r="M1" t="s" s="1">
-        <v>48</v>
-      </c>
-      <c r="N1" t="s" s="1">
-        <v>49</v>
-      </c>
-      <c r="O1" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="P1" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="Q1" t="s" s="1">
-        <v>52</v>
-      </c>
-      <c r="R1" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="S1" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="T1" t="s" s="1">
-        <v>55</v>
-      </c>
-      <c r="U1" t="s" s="1">
-        <v>56</v>
-      </c>
-      <c r="V1" t="s" s="1">
-        <v>57</v>
-      </c>
-      <c r="W1" t="s" s="1">
-        <v>58</v>
-      </c>
-      <c r="X1" t="s" s="1">
-        <v>59</v>
-      </c>
-      <c r="Y1" t="s" s="1">
-        <v>60</v>
-      </c>
-      <c r="Z1" t="s" s="1">
-        <v>61</v>
-      </c>
-      <c r="AA1" t="s" s="1">
-        <v>62</v>
-      </c>
-      <c r="AB1" t="s" s="1">
-        <v>63</v>
-      </c>
-      <c r="AC1" t="s" s="1">
-        <v>64</v>
-      </c>
-      <c r="AD1" t="s" s="1">
-        <v>65</v>
-      </c>
-      <c r="AE1" t="s" s="1">
-        <v>66</v>
-      </c>
-      <c r="AF1" t="s" s="1">
-        <v>67</v>
-      </c>
-      <c r="AG1" t="s" s="1">
-        <v>68</v>
-      </c>
-      <c r="AH1" t="s" s="1">
-        <v>69</v>
-      </c>
-      <c r="AI1" t="s" s="1">
-        <v>70</v>
-      </c>
-      <c r="AJ1" t="s" s="1">
-        <v>71</v>
-      </c>
-      <c r="AK1" t="s" s="1">
-        <v>72</v>
-      </c>
-      <c r="AL1" t="s" s="1">
-        <v>73</v>
-      </c>
-      <c r="AM1" t="s" s="1">
-        <v>74</v>
-      </c>
-      <c r="AN1" t="s" s="1">
-        <v>75</v>
+      <c r="AN1" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="N2" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="N2" t="s" s="2">
+        <v>51</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="N4" t="s" s="2">
+        <v>63</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="G6" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>107</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>117</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O9" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="O9" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="P9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="P11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>161</v>
-      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="P14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O15" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>76</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>183</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>66</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>76</v>
+        <v>167</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q19" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="Q19" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="R19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q20" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>223</v>
+        <v>36</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>224</v>
+        <v>36</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>36</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>36</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>229</v>
+        <v>124</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>251</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>268</v>
+        <v>36</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>235</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>271</v>
+        <v>36</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>277</v>
+        <v>152</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>76</v>
+        <v>250</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>76</v>
+        <v>255</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="P30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>288</v>
+        <v>36</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>289</v>
+        <v>36</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>290</v>
+        <v>36</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>295</v>
+        <v>36</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="P31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>301</v>
+        <v>36</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>307</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>76</v>
+        <v>274</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>308</v>
+        <v>36</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>76</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>281</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>322</v>
+        <v>290</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>324</v>
+        <v>36</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>329</v>
+        <v>36</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>332</v>
+        <v>189</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>335</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>301</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>338</v>
+        <v>95</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>341</v>
+        <v>36</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>342</v>
+        <v>302</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>133</v>
+        <v>307</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="P38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>342</v>
+        <v>91</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>347</v>
+        <v>36</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>312</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>143</v>
+        <v>315</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>131</v>
+        <v>316</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>353</v>
+        <v>319</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>363</v>
+        <v>328</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>329</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>76</v>
+        <v>330</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>365</v>
+        <v>292</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>367</v>
+        <v>332</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>364</v>
+        <v>329</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>370</v>
+        <v>36</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>332</v>
+        <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>371</v>
+        <v>298</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>372</v>
+        <v>299</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>373</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>369</v>
+        <v>300</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>301</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>374</v>
+        <v>302</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>338</v>
+        <v>95</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>341</v>
+        <v>36</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>342</v>
+        <v>302</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>376</v>
+        <v>337</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>376</v>
+        <v>337</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>133</v>
+        <v>307</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="P45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>342</v>
+        <v>91</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>137</v>
+        <v>342</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>143</v>
+        <v>343</v>
       </c>
       <c r="P46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>76</v>
+        <v>344</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>131</v>
+        <v>334</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>379</v>
+        <v>36</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>346</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>384</v>
+        <v>36</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>349</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>349</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>292</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>349</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>332</v>
+        <v>189</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>390</v>
+        <v>298</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>391</v>
+        <v>299</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>392</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>301</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>374</v>
+        <v>302</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>338</v>
+        <v>95</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>341</v>
+        <v>36</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>342</v>
+        <v>302</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>133</v>
+        <v>307</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="P51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>342</v>
+        <v>91</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>356</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>356</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>143</v>
+        <v>359</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>76</v>
+        <v>360</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>131</v>
+        <v>334</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>396</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>396</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>379</v>
+        <v>36</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>192</v>
+        <v>346</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="P53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>400</v>
+        <v>36</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>396</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>386</v>
+        <v>264</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>366</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>76</v>
+        <v>268</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>374</v>
+        <v>269</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>405</v>
+        <v>368</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>368</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>368</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>308</v>
+        <v>268</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>304</v>
+        <v>372</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>76</v>
+        <v>376</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>76</v>
+        <v>377</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>308</v>
+        <v>378</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>309</v>
+        <v>379</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>412</v>
+        <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="U57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="V57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="W57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>416</v>
+        <v>36</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>417</v>
+        <v>36</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>418</v>
+        <v>378</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>419</v>
+        <v>379</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN58">
+  <autoFilter ref="A1:AN57">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8321,7 +8078,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI57">
+  <conditionalFormatting sqref="A2:AI56">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
